--- a/changes/replus-runtime-v5/candidates/RPL_ROOM.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_ROOM.xlsx
@@ -1,37 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="90_Evidence" sheetId="1" r:id="R56857d669630409a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_INDEX" sheetId="2" r:id="R027c787beb294f5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_README" sheetId="3" r:id="R36e7744c9df14a75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_入力フロー" sheetId="4" r:id="R188f2361751f4e3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_取替方式" sheetId="5" r:id="Rdb1b859c5b664f12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02A_仕様区分" sheetId="6" r:id="R06f00dbbd12249c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_窓種" sheetId="7" r:id="R776f59abcfe743df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03A_枠仕様" sheetId="8" r:id="Rdfd34bfa6f7d46d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03B_窓種枠設定" sheetId="9" r:id="R4778e140562144e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_窓種固有仕様" sheetId="10" r:id="Rd72aedaef4634c85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_サイズルール" sheetId="11" r:id="R52aa4c2f31d0400c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05A_サイズ区間" sheetId="12" r:id="R22a4c8f21a4a4d72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05B_境界ルール" sheetId="13" r:id="R0175e008a1ec4771"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_色" sheetId="14" r:id="Rd310e4169bbc4ade"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06A_色適用条件" sheetId="15" r:id="Rf4ba1fdf166048fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_網戸" sheetId="16" r:id="R9f890b0e7fb44c30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07A_網戸適用条件" sheetId="17" r:id="Reac65b208cd0455f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_ガラス" sheetId="18" r:id="R048bb73c0131431c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08A_ガラス適用条件" sheetId="19" r:id="R3e48865b6aeb4d5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_その他OP" sheetId="20" r:id="Rc865b8c65a3348a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09A_OP依存関係" sheetId="21" r:id="R3aea0d17a14a429b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_適用条件" sheetId="22" r:id="Rd8e7ae5687794235"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10A_既設窓互換" sheetId="23" r:id="R7aea1165a81944b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10B_現調項目" sheetId="24" r:id="R8d4579dd318d47a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_QA" sheetId="25" r:id="Rc82afc2005f34d2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04A_開口構成" sheetId="26" r:id="R466e4a5c3781466d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_見積入力テスト" sheetId="27" r:id="R8053414ab145457f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10C_化粧カバー見付" sheetId="28" r:id="R2486f5c36d844345"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="90_Evidence" sheetId="1" r:id="R56857d669630409a"/>
+    <sheet name="00_INDEX" sheetId="2" r:id="R027c787beb294f5d"/>
+    <sheet name="00_README" sheetId="3" r:id="R36e7744c9df14a75"/>
+    <sheet name="01_入力フロー" sheetId="4" r:id="R188f2361751f4e3d"/>
+    <sheet name="02_取替方式" sheetId="5" r:id="Rdb1b859c5b664f12"/>
+    <sheet name="02A_仕様区分" sheetId="6" r:id="R06f00dbbd12249c0"/>
+    <sheet name="03_窓種" sheetId="7" r:id="R776f59abcfe743df"/>
+    <sheet name="03A_枠仕様" sheetId="8" r:id="Rdfd34bfa6f7d46d7"/>
+    <sheet name="03B_窓種枠設定" sheetId="9" r:id="R4778e140562144e4"/>
+    <sheet name="04_窓種固有仕様" sheetId="10" r:id="Rd72aedaef4634c85"/>
+    <sheet name="05_サイズルール" sheetId="11" r:id="R52aa4c2f31d0400c"/>
+    <sheet name="05A_サイズ区間" sheetId="12" r:id="R22a4c8f21a4a4d72"/>
+    <sheet name="05B_境界ルール" sheetId="13" r:id="R0175e008a1ec4771"/>
+    <sheet name="06_色" sheetId="14" r:id="Rd310e4169bbc4ade"/>
+    <sheet name="06A_色適用条件" sheetId="15" r:id="Rf4ba1fdf166048fb"/>
+    <sheet name="07_網戸" sheetId="16" r:id="R9f890b0e7fb44c30"/>
+    <sheet name="07A_網戸適用条件" sheetId="17" r:id="Reac65b208cd0455f"/>
+    <sheet name="08_ガラス" sheetId="18" r:id="R048bb73c0131431c"/>
+    <sheet name="08A_ガラス適用条件" sheetId="19" r:id="R3e48865b6aeb4d5a"/>
+    <sheet name="09_その他OP" sheetId="20" r:id="Rc865b8c65a3348a6"/>
+    <sheet name="09A_OP依存関係" sheetId="21" r:id="R3aea0d17a14a429b"/>
+    <sheet name="10_適用条件" sheetId="22" r:id="Rd8e7ae5687794235"/>
+    <sheet name="10A_既設窓互換" sheetId="23" r:id="R7aea1165a81944b8"/>
+    <sheet name="10B_現調項目" sheetId="24" r:id="R8d4579dd318d47a6"/>
+    <sheet name="99_QA" sheetId="25" r:id="Rc82afc2005f34d2b"/>
+    <sheet name="04A_開口構成" sheetId="26" r:id="R466e4a5c3781466d"/>
+    <sheet name="11_見積入力テスト" sheetId="27" r:id="R8053414ab145457f"/>
+    <sheet name="10C_化粧カバー見付" sheetId="28" r:id="R2486f5c36d844345"/>
+    <sheet name="14_UI選択契約" sheetId="29" r:id="rIdReplusUiV9"/>
+  </sheets>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -980,6 +981,721 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/replus-ui-v9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str" s="35">
+        <v>リプラス住宅用・共通UI選択契約</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="37"/>
+      <c r="F1"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="str" s="32">
+        <v>分類</v>
+      </c>
+      <c r="B2" t="str" s="33">
+        <v>対象</v>
+      </c>
+      <c r="C2" t="str" s="33">
+        <v>依存元</v>
+      </c>
+      <c r="D2" t="str" s="33">
+        <v>処理</v>
+      </c>
+      <c r="E2" t="str" s="34">
+        <v>根拠区分</v>
+      </c>
+      <c r="F2" t="str">
+        <v>revision</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str" s="35">
+        <v>色連動</v>
+      </c>
+      <c r="B3" t="str" s="36">
+        <v>sash_interior_color</v>
+      </c>
+      <c r="C3" t="str" s="36">
+        <v>color_mode,sash_exterior_color</v>
+      </c>
+      <c r="D3" t="str" s="36">
+        <v>{"targetField": "sash_interior_color", "applicability": {"color_mode": "SAME"}, "parents": ["color_mode", "sash_exterior_color"], "cases": [{"when": {"sash_exterior_color": "T"}, "value": "M"}, {"when": {"sash_exterior_color": "G"}, "value": "G"}, {"when": {"sash_exterior_color": "K"}, "value": "K"}, {"when": {"sash_exterior_color": "D"}, "value": "D"}, {"when": {"sash_exterior_color": "W"}, "value": "W"}], "resolvedMessage": "外観色に連動しています。", "pendingMessage": "本体外観色を選択してください。", "unavailableMessage": "本体内観色の対応を確認してください。"}</v>
+      </c>
+      <c r="E3" t="str" s="37">
+        <v>USER_APPLICATION_POLICY</v>
+      </c>
+      <c r="F3" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str" s="35">
+        <v>色連動</v>
+      </c>
+      <c r="B4" t="str" s="36">
+        <v>exterior_cover_color</v>
+      </c>
+      <c r="C4" t="str" s="36">
+        <v>sash_exterior_color</v>
+      </c>
+      <c r="D4" t="str" s="36">
+        <v>{"targetField": "exterior_cover_color", "parents": ["sash_exterior_color"], "cases": [{"when": {"sash_exterior_color": "T"}, "value": "T"}, {"when": {"sash_exterior_color": "G"}, "value": "G"}, {"when": {"sash_exterior_color": "K"}, "value": "K"}, {"when": {"sash_exterior_color": "D"}, "value": "D"}, {"when": {"sash_exterior_color": "W"}, "value": "W"}], "resolvedMessage": "本体外観色に連動しています。", "pendingMessage": "サッシ本体の色を選択してください。", "unavailableMessage": "本体色に対応するカバー部材の確認が必要です。"}</v>
+      </c>
+      <c r="E4" t="str" s="37">
+        <v>USER_APPLICATION_POLICY</v>
+      </c>
+      <c r="F4" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str" s="35">
+        <v>色連動</v>
+      </c>
+      <c r="B5" t="str" s="36">
+        <v>interior_cover_color</v>
+      </c>
+      <c r="C5" t="str" s="36">
+        <v>sash_interior_color</v>
+      </c>
+      <c r="D5" t="str" s="36">
+        <v>{"targetField": "interior_cover_color", "parents": ["sash_interior_color"], "cases": [{"when": {"sash_interior_color": "M"}, "value": "M"}, {"when": {"sash_interior_color": "G"}, "value": "G"}, {"when": {"sash_interior_color": "K"}, "value": "K"}, {"when": {"sash_interior_color": "D"}, "value": "D"}, {"when": {"sash_interior_color": "W"}, "value": "W"}, {"when": {"sash_interior_color": "C"}, "value": "C"}, {"when": {"sash_interior_color": "B"}, "value": "B"}, {"when": {"sash_interior_color": "P"}, "value": "P"}, {"when": {"sash_interior_color": "F"}, "value": "F"}], "resolvedMessage": "本体内観色に連動しています。", "pendingMessage": "サッシ本体の色を選択してください。", "unavailableMessage": "本体色に対応するカバー部材の確認が必要です。"}</v>
+      </c>
+      <c r="E5" t="str" s="37">
+        <v>USER_APPLICATION_POLICY</v>
+      </c>
+      <c r="F5" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B6" t="str" s="36">
+        <v>window_type</v>
+      </c>
+      <c r="C6" t="str" s="36"/>
+      <c r="D6" t="str" s="36">
+        <v>{"label": "窓種", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E6" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F6" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B7" t="str" s="36">
+        <v>frame_type</v>
+      </c>
+      <c r="C7" t="str" s="36">
+        <v>window_type</v>
+      </c>
+      <c r="D7" t="str" s="36">
+        <v>{"label": "枠仕様", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E7" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F7" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B8" t="str" s="36">
+        <v>spec_panel_configuration</v>
+      </c>
+      <c r="C8" t="str" s="36">
+        <v>window_type</v>
+      </c>
+      <c r="D8" t="str" s="36">
+        <v>{"label": "建数", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E8" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F8" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B9" t="str" s="36">
+        <v>spec_height_category</v>
+      </c>
+      <c r="C9" t="str" s="36">
+        <v>window_type,custom_width,custom_height</v>
+      </c>
+      <c r="D9" t="str" s="36">
+        <v>{"label": "マド／テラス", "group": "opening", "internal": true}</v>
+      </c>
+      <c r="E9" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F9" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B10" t="str" s="36">
+        <v>spec_sash_configuration</v>
+      </c>
+      <c r="C10" t="str" s="36">
+        <v>spec_height_category,spec_panel_configuration,window_type</v>
+      </c>
+      <c r="D10" t="str" s="36">
+        <v>{"label": "障子仕様", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E10" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F10" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B11" t="str" s="36">
+        <v>spec_opening_form</v>
+      </c>
+      <c r="C11" t="str" s="36">
+        <v>window_type</v>
+      </c>
+      <c r="D11" t="str" s="36">
+        <v>{"label": "開口形式", "group": "opening", "internal": false}</v>
+      </c>
+      <c r="E11" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F11" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B12" t="str" s="36">
+        <v>screen</v>
+      </c>
+      <c r="C12" t="str" s="36">
+        <v>spec_height_category,window_type</v>
+      </c>
+      <c r="D12" t="str" s="36">
+        <v>{"label": "網戸", "group": "screen", "internal": false}</v>
+      </c>
+      <c r="E12" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F12" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B13" t="str" s="36">
+        <v>size_mode</v>
+      </c>
+      <c r="C13" t="str" s="36"/>
+      <c r="D13" t="str" s="36">
+        <v>{"label": "寸法の指定方法", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E13" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F13" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B14" t="str" s="36">
+        <v>custom_width</v>
+      </c>
+      <c r="C14" t="str" s="36">
+        <v>size_mode</v>
+      </c>
+      <c r="D14" t="str" s="36">
+        <v>{"label": "製品仕上がり幅 W（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E14" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F14" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B15" t="str" s="36">
+        <v>custom_height</v>
+      </c>
+      <c r="C15" t="str" s="36">
+        <v>size_mode</v>
+      </c>
+      <c r="D15" t="str" s="36">
+        <v>{"label": "製品仕上がり高さ H（mm）", "group": "size", "internal": false}</v>
+      </c>
+      <c r="E15" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F15" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B16" t="str" s="36">
+        <v>sash_exterior_color</v>
+      </c>
+      <c r="C16" t="str" s="36"/>
+      <c r="D16" t="str" s="36">
+        <v>{"label": "本体外観色", "group": "finish", "internal": false}</v>
+      </c>
+      <c r="E16" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F16" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B17" t="str" s="36">
+        <v>sash_interior_color</v>
+      </c>
+      <c r="C17" t="str" s="36">
+        <v>color_mode,sash_exterior_color</v>
+      </c>
+      <c r="D17" t="str" s="36">
+        <v>{"label": "本体内観色", "group": "finish", "internal": false}</v>
+      </c>
+      <c r="E17" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F17" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B18" t="str" s="36">
+        <v>exterior_cover_color</v>
+      </c>
+      <c r="C18" t="str" s="36">
+        <v>sash_exterior_color</v>
+      </c>
+      <c r="D18" t="str" s="36">
+        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
+      </c>
+      <c r="E18" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F18" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B19" t="str" s="36">
+        <v>interior_cover_color</v>
+      </c>
+      <c r="C19" t="str" s="36">
+        <v>sash_interior_color</v>
+      </c>
+      <c r="D19" t="str" s="36">
+        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
+      </c>
+      <c r="E19" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F19" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B20" t="str" s="36">
+        <v>wooden_casing_color</v>
+      </c>
+      <c r="C20" t="str" s="36">
+        <v>options</v>
+      </c>
+      <c r="D20" t="str" s="36">
+        <v>{"label": "木製ケーシング色", "group": "part_detail", "internal": false}</v>
+      </c>
+      <c r="E20" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F20" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B21" t="str" s="36">
+        <v>options</v>
+      </c>
+      <c r="C21" t="str" s="36">
+        <v>window_type</v>
+      </c>
+      <c r="D21" t="str" s="36">
+        <v>{"label": "追加部材・オプション", "group": "options", "internal": false}</v>
+      </c>
+      <c r="E21" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F21" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B22" t="str" s="36">
+        <v>usage_humidity</v>
+      </c>
+      <c r="C22" t="str" s="36"/>
+      <c r="D22" t="str" s="36">
+        <v>{"label": "使用環境", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E22" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F22" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B23" t="str" s="36">
+        <v>building_structure</v>
+      </c>
+      <c r="C23" t="str" s="36"/>
+      <c r="D23" t="str" s="36">
+        <v>{"label": "建物構造", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E23" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F23" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B24" t="str" s="36">
+        <v>installation_room</v>
+      </c>
+      <c r="C24" t="str" s="36"/>
+      <c r="D24" t="str" s="36">
+        <v>{"label": "設置場所", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E24" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F24" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B25" t="str" s="36">
+        <v>work_space</v>
+      </c>
+      <c r="C25" t="str" s="36"/>
+      <c r="D25" t="str" s="36">
+        <v>{"label": "新設枠の振出し条件", "group": "context", "internal": false}</v>
+      </c>
+      <c r="E25" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F25" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B26" t="str" s="36">
+        <v>glass_category</v>
+      </c>
+      <c r="C26" t="str" s="36">
+        <v>window_type,frame_type</v>
+      </c>
+      <c r="D26" t="str" s="36">
+        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E26" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F26" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B27" t="str" s="36">
+        <v>glass</v>
+      </c>
+      <c r="C27" t="str" s="36">
+        <v>glass_category,window_type,frame_type</v>
+      </c>
+      <c r="D27" t="str" s="36">
+        <v>{"label": "ガラス詳細・Low-E仕様", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E27" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F27" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B28" t="str" s="36">
+        <v>glass_gas</v>
+      </c>
+      <c r="C28" t="str" s="36">
+        <v>frame_type,glass_category</v>
+      </c>
+      <c r="D28" t="str" s="36">
+        <v>{"label": "中空層", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E28" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F28" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B29" t="str" s="36">
+        <v>glass_spacer</v>
+      </c>
+      <c r="C29" t="str" s="36">
+        <v>frame_type,glass_category,glass_gas</v>
+      </c>
+      <c r="D29" t="str" s="36">
+        <v>{"label": "スペーサー", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E29" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F29" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B30" t="str" s="36">
+        <v>glass_function</v>
+      </c>
+      <c r="C30" t="str" s="36">
+        <v>glass_category,glass,window_type</v>
+      </c>
+      <c r="D30" t="str" s="36">
+        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E30" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F30" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B31" t="str" s="36">
+        <v>glass_appearance</v>
+      </c>
+      <c r="C31" t="str" s="36">
+        <v>glass,glass_function</v>
+      </c>
+      <c r="D31" t="str" s="36">
+        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
+      </c>
+      <c r="E31" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F31" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B32" t="str" s="36">
+        <v>color_mode</v>
+      </c>
+      <c r="C32" t="str" s="36"/>
+      <c r="D32" t="str" s="36">
+        <v>{"label": "本体の色設定", "group": "finish", "internal": false}</v>
+      </c>
+      <c r="E32" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F32" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B33" t="str" s="36">
+        <v>interior_cover_type</v>
+      </c>
+      <c r="C33" t="str" s="36"/>
+      <c r="D33" t="str" s="36">
+        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false}</v>
+      </c>
+      <c r="E33" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F33" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B34" t="str" s="36">
+        <v>exterior_cover_type</v>
+      </c>
+      <c r="C34" t="str" s="36">
+        <v>frame_type,survey_cover_top,survey_cover_bottom,survey_cover_side</v>
+      </c>
+      <c r="D34" t="str" s="36">
+        <v>{"label": "化粧カバーの大きさ・組合せ", "group": "exterior_finish", "internal": false}</v>
+      </c>
+      <c r="E34" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F34" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B35" t="str" s="36">
+        <v>survey_cover_top</v>
+      </c>
+      <c r="C35" t="str" s="36"/>
+      <c r="D35" t="str" s="36">
+        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E35" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F35" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B36" t="str" s="36">
+        <v>survey_cover_bottom</v>
+      </c>
+      <c r="C36" t="str" s="36"/>
+      <c r="D36" t="str" s="36">
+        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E36" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F36" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str" s="35">
+        <v>フロー</v>
+      </c>
+      <c r="B37" t="str" s="36">
+        <v>survey_cover_side</v>
+      </c>
+      <c r="C37" t="str" s="36"/>
+      <c r="D37" t="str" s="36">
+        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false}</v>
+      </c>
+      <c r="E37" t="str" s="37">
+        <v>UI_PRESENTATION</v>
+      </c>
+      <c r="F37" t="str">
+        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
@@ -10827,269 +11543,356 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="60" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>01_入力フロー｜居室仕様</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-    </x:row>
-    <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="32" t="str">
-        <x:v>順序</x:v>
-      </x:c>
-      <x:c r="B3" s="33" t="str">
-        <x:v>表示項目</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="str">
-        <x:v>データキー</x:v>
-      </x:c>
-      <x:c r="D3" s="33" t="str">
-        <x:v>候補/入力</x:v>
-      </x:c>
-      <x:c r="E3" s="34" t="str">
-        <x:v>制御方針</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="35" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="36" t="str">
-        <x:v>取替方式</x:v>
-      </x:c>
-      <x:c r="C4" s="36" t="str">
-        <x:v>installation_system_id</x:v>
-      </x:c>
-      <x:c r="D4" s="36" t="str">
-        <x:v>RPL_DIRECT</x:v>
-      </x:c>
-      <x:c r="E4" s="37" t="str">
-        <x:v>今回固定。将来アタッチ枠/汎用カットモールへ分岐</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="35" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="36" t="str">
-        <x:v>仕様区分</x:v>
-      </x:c>
-      <x:c r="C5" s="36" t="str">
-        <x:v>variation_id</x:v>
-      </x:c>
-      <x:c r="D5" s="36" t="str">
-        <x:v>RPL_ROOM</x:v>
-      </x:c>
-      <x:c r="E5" s="37" t="str">
-        <x:v>今回固定。TWタイプ/EWタイプ/浴室仕様は別variation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="35" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="36" t="str">
-        <x:v>開口構成</x:v>
-      </x:c>
-      <x:c r="C6" s="36" t="str">
-        <x:v>opening_configuration</x:v>
-      </x:c>
-      <x:c r="D6" s="36" t="str">
-        <x:v>SINGLE</x:v>
-      </x:c>
-      <x:c r="E6" s="37" t="str">
-        <x:v>単窓を優先。連窓/段窓は別ルール</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="35" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="36" t="str">
-        <x:v>窓種</x:v>
-      </x:c>
-      <x:c r="C7" s="36" t="str">
-        <x:v>window_type_id</x:v>
-      </x:c>
-      <x:c r="D7" s="36" t="str">
-        <x:v>8窓種</x:v>
-      </x:c>
-      <x:c r="E7" s="37" t="str">
-        <x:v>操作方式が商品体系を変えるものは窓種IDに含める</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="35" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="36" t="str">
-        <x:v>枠仕様</x:v>
-      </x:c>
-      <x:c r="C8" s="36" t="str">
-        <x:v>frame_type_id</x:v>
-      </x:c>
-      <x:c r="D8" s="36" t="str">
-        <x:v>STD / BRIDGE</x:v>
-      </x:c>
-      <x:c r="E8" s="37" t="str">
-        <x:v>BRIDGEは引違い窓だけ表示</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="35" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B9" s="36" t="str">
-        <x:v>窓種固有仕様</x:v>
-      </x:c>
-      <x:c r="C9" s="36" t="str">
-        <x:v>solid_spec</x:v>
-      </x:c>
-      <x:c r="D9" s="36" t="str">
-        <x:v>2枚建/4枚建、マド/テラス等</x:v>
-      </x:c>
-      <x:c r="E9" s="37" t="str">
-        <x:v>該当窓種だけ表示</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="35" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B10" s="36" t="str">
-        <x:v>採寸W/H</x:v>
-      </x:c>
-      <x:c r="C10" s="36" t="str">
-        <x:v>survey_w / survey_h</x:v>
-      </x:c>
-      <x:c r="D10" s="36" t="str">
-        <x:v>現場入力</x:v>
-      </x:c>
-      <x:c r="E10" s="37" t="str">
-        <x:v>3箇所採寸・既設状態確認を別レイヤーで管理</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="35" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B11" s="36" t="str">
-        <x:v>出来寸W/H</x:v>
-      </x:c>
-      <x:c r="C11" s="36" t="str">
-        <x:v>finished_w / finished_h</x:v>
-      </x:c>
-      <x:c r="D11" s="36" t="str">
-        <x:v>自動算出</x:v>
-      </x:c>
-      <x:c r="E11" s="37" t="str">
-        <x:v>WD=WS-10、HD=HS-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="35" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B12" s="36" t="str">
-        <x:v>色</x:v>
-      </x:c>
-      <x:c r="C12" s="36" t="str">
-        <x:v>color_mode / colors</x:v>
-      </x:c>
-      <x:c r="D12" s="36" t="str">
-        <x:v>同一/組合せ自由</x:v>
-      </x:c>
-      <x:c r="E12" s="37" t="str">
-        <x:v>サッシ色とカバー色を分離</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="35" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B13" s="36" t="str">
-        <x:v>網戸</x:v>
-      </x:c>
-      <x:c r="C13" s="36" t="str">
-        <x:v>screen_type / mesh</x:v>
-      </x:c>
-      <x:c r="D13" s="36" t="str">
-        <x:v>窓種連動</x:v>
-      </x:c>
-      <x:c r="E13" s="37" t="str">
-        <x:v>引違い用中桟を他窓種へ流用しない</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="35" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B14" s="36" t="str">
-        <x:v>ガラス</x:v>
-      </x:c>
-      <x:c r="C14" s="36" t="str">
-        <x:v>glass_category / detail</x:v>
-      </x:c>
-      <x:c r="D14" s="36" t="str">
-        <x:v>窓種連動</x:v>
-      </x:c>
-      <x:c r="E14" s="37" t="str">
-        <x:v>上げ下げ窓FSのみトリプル追加あり</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="35" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B15" s="36" t="str">
-        <x:v>オプション</x:v>
-      </x:c>
-      <x:c r="C15" s="36" t="str">
-        <x:v>option_id</x:v>
-      </x:c>
-      <x:c r="D15" s="36" t="str">
-        <x:v>窓種・サイズ連動</x:v>
-      </x:c>
-      <x:c r="E15" s="37" t="str">
-        <x:v>OP依存関係で非対応候補を除外</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="38" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B16" s="39" t="str">
-        <x:v>現調/適用判定</x:v>
-      </x:c>
-      <x:c r="C16" s="39" t="str">
-        <x:v>applicability</x:v>
-      </x:c>
-      <x:c r="D16" s="39" t="str">
-        <x:v>別UI/判定レイヤー</x:v>
-      </x:c>
-      <x:c r="E16" s="40" t="str">
-        <x:v>既設材質・構造・防火・既設窓種など</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:E1"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="26" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="60" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" t="str" s="4">
+        <v>リプラス住宅用・グローバルセレクションフロー</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1"/>
+    </row>
+    <row r="2">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" t="str" s="32">
+        <v>順番</v>
+      </c>
+      <c r="B3" t="str" s="33">
+        <v>表示項目</v>
+      </c>
+      <c r="C3" t="str" s="33">
+        <v>データキー</v>
+      </c>
+      <c r="D3" t="str" s="33">
+        <v>候補/入力</v>
+      </c>
+      <c r="E3" t="str" s="34">
+        <v>制御方針</v>
+      </c>
+      <c r="F3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n" s="35">
+        <v>1</v>
+      </c>
+      <c r="B4" t="str" s="36">
+        <v>商品・リプラス仕様</v>
+      </c>
+      <c r="C4" t="str" s="36">
+        <v>product / specification</v>
+      </c>
+      <c r="D4" t="str" s="36">
+        <v>リプラス住宅用 → 仕様</v>
+      </c>
+      <c r="E4" t="str" s="37">
+        <v>今回承認されたアプリ運用ルール</v>
+      </c>
+      <c r="F4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n" s="35">
+        <v>2</v>
+      </c>
+      <c r="B5" t="str" s="36">
+        <v>設置・施工条件</v>
+      </c>
+      <c r="C5" t="str" s="36">
+        <v>context</v>
+      </c>
+      <c r="D5" t="str" s="36">
+        <v>選択・確認</v>
+      </c>
+      <c r="E5" t="str" s="37">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n" s="35">
+        <v>3</v>
+      </c>
+      <c r="B6" t="str" s="36">
+        <v>窓種・基本仕様</v>
+      </c>
+      <c r="C6" t="str" s="36">
+        <v>opening</v>
+      </c>
+      <c r="D6" t="str" s="36">
+        <v>選択・確認</v>
+      </c>
+      <c r="E6" t="str" s="37">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n" s="35">
+        <v>4</v>
+      </c>
+      <c r="B7" t="str" s="36">
+        <v>本体色</v>
+      </c>
+      <c r="C7" t="str" s="36">
+        <v>finish</v>
+      </c>
+      <c r="D7" t="str" s="36">
+        <v>選択・確認</v>
+      </c>
+      <c r="E7" t="str" s="37">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="35">
+        <v>5</v>
+      </c>
+      <c r="B8" t="str" s="36">
+        <v>網戸</v>
+      </c>
+      <c r="C8" t="str" s="36">
+        <v>screen</v>
+      </c>
+      <c r="D8" t="str" s="36">
+        <v>選択・確認</v>
+      </c>
+      <c r="E8" t="str" s="37">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="35">
+        <v>6</v>
+      </c>
+      <c r="B9" t="str" s="36">
+        <v>ガラス</v>
+      </c>
+      <c r="C9" t="str" s="36">
+        <v>glazing</v>
+      </c>
+      <c r="D9" t="str" s="36">
+        <v>選択・確認</v>
+      </c>
+      <c r="E9" t="str" s="37">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="35">
+        <v>7</v>
+      </c>
+      <c r="B10" t="str" s="36">
+        <v>室内側の仕上げ・アングルカバー</v>
+      </c>
+      <c r="C10" t="str" s="36">
+        <v>interior_finish</v>
+      </c>
+      <c r="D10" t="str" s="36">
+        <v>選択・確認</v>
+      </c>
+      <c r="E10" t="str" s="37">
+        <v>本体色に連動</v>
+      </c>
+      <c r="F10"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="35">
+        <v>8</v>
+      </c>
+      <c r="B11" t="str" s="36">
+        <v>室外側の仕上げ・化粧カバー</v>
+      </c>
+      <c r="C11" t="str" s="36">
+        <v>exterior_finish</v>
+      </c>
+      <c r="D11" t="str" s="36">
+        <v>選択・確認</v>
+      </c>
+      <c r="E11" t="str" s="37">
+        <v>本体色に連動</v>
+      </c>
+      <c r="F11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="35">
+        <v>9</v>
+      </c>
+      <c r="B12" t="str" s="36">
+        <v>新設サッシのオプション</v>
+      </c>
+      <c r="C12" t="str" s="36">
+        <v>native_options</v>
+      </c>
+      <c r="D12" t="str" s="36">
+        <v>選択・確認</v>
+      </c>
+      <c r="E12" t="str" s="37">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="35">
+        <v>10</v>
+      </c>
+      <c r="B13" t="str" s="36">
+        <v>追加部材・オプション</v>
+      </c>
+      <c r="C13" t="str" s="36">
+        <v>options</v>
+      </c>
+      <c r="D13" t="str" s="36">
+        <v>選択・確認</v>
+      </c>
+      <c r="E13" t="str" s="37">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="35">
+        <v>11</v>
+      </c>
+      <c r="B14" t="str" s="36">
+        <v>選択した部材の仕様</v>
+      </c>
+      <c r="C14" t="str" s="36">
+        <v>part_detail</v>
+      </c>
+      <c r="D14" t="str" s="36">
+        <v>選択・確認</v>
+      </c>
+      <c r="E14" t="str" s="37">
+        <v>対応する項目のみ表示</v>
+      </c>
+      <c r="F14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="35">
+        <v>12</v>
+      </c>
+      <c r="B15" t="str" s="36">
+        <v>現場採寸・取付条件</v>
+      </c>
+      <c r="C15" t="str" s="36">
+        <v>survey</v>
+      </c>
+      <c r="D15" t="str" s="36">
+        <v>選択・確認</v>
+      </c>
+      <c r="E15" t="str" s="37">
+        <v>採寸後に再評価</v>
+      </c>
+      <c r="F15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="38">
+        <v>13</v>
+      </c>
+      <c r="B16" t="str" s="39">
+        <v>製品寸法</v>
+      </c>
+      <c r="C16" t="str" s="39">
+        <v>size</v>
+      </c>
+      <c r="D16" t="str" s="39">
+        <v>選択・確認</v>
+      </c>
+      <c r="E16" t="str" s="40">
+        <v>採寸後に再評価</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+    </row>
+    <row r="18">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+    </row>
+    <row r="19">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+    </row>
+    <row r="20">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+    </row>
+    <row r="21">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+    </row>
+    <row r="22">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+    </row>
+    <row r="23">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+    </row>
+    <row r="24">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>

--- a/changes/replus-runtime-v5/candidates/RPL_ROOM.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_ROOM.xlsx
@@ -1032,7 +1032,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1052,7 +1052,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1072,7 +1072,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1090,7 +1090,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1110,7 +1110,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1130,7 +1130,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1150,7 +1150,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1170,7 +1170,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1210,7 +1210,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1228,7 +1228,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1248,7 +1248,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1268,7 +1268,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1286,7 +1286,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1306,7 +1306,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1326,7 +1326,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1366,7 +1366,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1386,7 +1386,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1398,13 +1398,13 @@
       </c>
       <c r="C22" t="str" s="36"/>
       <c r="D22" t="str" s="36">
-        <v>{"label": "使用環境", "group": "context", "internal": false}</v>
+        <v>{"label": "使用環境", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E22" t="str" s="37">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1416,13 +1416,13 @@
       </c>
       <c r="C23" t="str" s="36"/>
       <c r="D23" t="str" s="36">
-        <v>{"label": "建物構造", "group": "context", "internal": false}</v>
+        <v>{"label": "建物構造", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E23" t="str" s="37">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1434,13 +1434,13 @@
       </c>
       <c r="C24" t="str" s="36"/>
       <c r="D24" t="str" s="36">
-        <v>{"label": "設置場所", "group": "context", "internal": false}</v>
+        <v>{"label": "設置場所", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E24" t="str" s="37">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1452,13 +1452,13 @@
       </c>
       <c r="C25" t="str" s="36"/>
       <c r="D25" t="str" s="36">
-        <v>{"label": "新設枠の振出し条件", "group": "context", "internal": false}</v>
+        <v>{"label": "新設枠の振出し条件", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E25" t="str" s="37">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1478,7 +1478,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1498,7 +1498,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1518,7 +1518,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -1538,7 +1538,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -1558,7 +1558,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -1578,7 +1578,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -1596,7 +1596,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -1614,7 +1614,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="34">
@@ -1634,7 +1634,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F34" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="35">
@@ -1646,13 +1646,13 @@
       </c>
       <c r="C35" t="str" s="36"/>
       <c r="D35" t="str" s="36">
-        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E35" t="str" s="37">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F35" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="36">
@@ -1664,13 +1664,13 @@
       </c>
       <c r="C36" t="str" s="36"/>
       <c r="D36" t="str" s="36">
-        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E36" t="str" s="37">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F36" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
     <row r="37">
@@ -1682,13 +1682,13 @@
       </c>
       <c r="C37" t="str" s="36"/>
       <c r="D37" t="str" s="36">
-        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false}</v>
+        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
       </c>
       <c r="E37" t="str" s="37">
-        <v>UI_PRESENTATION</v>
+        <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F37" t="str">
-        <v>REPLUS_GLOBAL_FLOW_V9_20261014</v>
+        <v>REPLUS_SALES_FLOW_V10_20261014</v>
       </c>
     </row>
   </sheetData>
@@ -11612,10 +11612,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="str" s="36">
-        <v>設置・施工条件</v>
+        <v>窓種・基本仕様</v>
       </c>
       <c r="C5" t="str" s="36">
-        <v>context</v>
+        <v>opening</v>
       </c>
       <c r="D5" t="str" s="36">
         <v>選択・確認</v>
@@ -11630,10 +11630,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="str" s="36">
-        <v>窓種・基本仕様</v>
+        <v>本体色</v>
       </c>
       <c r="C6" t="str" s="36">
-        <v>opening</v>
+        <v>finish</v>
       </c>
       <c r="D6" t="str" s="36">
         <v>選択・確認</v>
@@ -11648,10 +11648,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="str" s="36">
-        <v>本体色</v>
+        <v>網戸</v>
       </c>
       <c r="C7" t="str" s="36">
-        <v>finish</v>
+        <v>screen</v>
       </c>
       <c r="D7" t="str" s="36">
         <v>選択・確認</v>
@@ -11666,10 +11666,10 @@
         <v>5</v>
       </c>
       <c r="B8" t="str" s="36">
-        <v>網戸</v>
+        <v>ガラス</v>
       </c>
       <c r="C8" t="str" s="36">
-        <v>screen</v>
+        <v>glazing</v>
       </c>
       <c r="D8" t="str" s="36">
         <v>選択・確認</v>
@@ -11684,16 +11684,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="str" s="36">
-        <v>ガラス</v>
+        <v>室内側の仕上げ・アングルカバー</v>
       </c>
       <c r="C9" t="str" s="36">
-        <v>glazing</v>
+        <v>interior_finish</v>
       </c>
       <c r="D9" t="str" s="36">
         <v>選択・確認</v>
       </c>
       <c r="E9" t="str" s="37">
-        <v>対応する項目のみ表示</v>
+        <v>本体色に連動</v>
       </c>
       <c r="F9"/>
     </row>
@@ -11702,10 +11702,10 @@
         <v>7</v>
       </c>
       <c r="B10" t="str" s="36">
-        <v>室内側の仕上げ・アングルカバー</v>
+        <v>室外側の仕上げ・化粧カバー</v>
       </c>
       <c r="C10" t="str" s="36">
-        <v>interior_finish</v>
+        <v>exterior_finish</v>
       </c>
       <c r="D10" t="str" s="36">
         <v>選択・確認</v>
@@ -11720,16 +11720,16 @@
         <v>8</v>
       </c>
       <c r="B11" t="str" s="36">
-        <v>室外側の仕上げ・化粧カバー</v>
+        <v>追加部材・オプション</v>
       </c>
       <c r="C11" t="str" s="36">
-        <v>exterior_finish</v>
+        <v>options</v>
       </c>
       <c r="D11" t="str" s="36">
         <v>選択・確認</v>
       </c>
       <c r="E11" t="str" s="37">
-        <v>本体色に連動</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F11"/>
     </row>
@@ -11738,10 +11738,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="str" s="36">
-        <v>新設サッシのオプション</v>
+        <v>選択した部材の仕様</v>
       </c>
       <c r="C12" t="str" s="36">
-        <v>native_options</v>
+        <v>part_detail</v>
       </c>
       <c r="D12" t="str" s="36">
         <v>選択・確認</v>
@@ -11756,71 +11756,41 @@
         <v>10</v>
       </c>
       <c r="B13" t="str" s="36">
-        <v>追加部材・オプション</v>
+        <v>製品寸法</v>
       </c>
       <c r="C13" t="str" s="36">
-        <v>options</v>
+        <v>size</v>
       </c>
       <c r="D13" t="str" s="36">
         <v>選択・確認</v>
       </c>
       <c r="E13" t="str" s="37">
-        <v>対応する項目のみ表示</v>
+        <v>採寸後に再評価</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14">
-      <c r="A14" t="n" s="35">
-        <v>11</v>
-      </c>
-      <c r="B14" t="str" s="36">
-        <v>選択した部材の仕様</v>
-      </c>
-      <c r="C14" t="str" s="36">
-        <v>part_detail</v>
-      </c>
-      <c r="D14" t="str" s="36">
-        <v>選択・確認</v>
-      </c>
-      <c r="E14" t="str" s="37">
-        <v>対応する項目のみ表示</v>
-      </c>
+      <c r="A14" s="35"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="37"/>
       <c r="F14"/>
     </row>
     <row r="15">
-      <c r="A15" t="n" s="35">
-        <v>12</v>
-      </c>
-      <c r="B15" t="str" s="36">
-        <v>現場採寸・取付条件</v>
-      </c>
-      <c r="C15" t="str" s="36">
-        <v>survey</v>
-      </c>
-      <c r="D15" t="str" s="36">
-        <v>選択・確認</v>
-      </c>
-      <c r="E15" t="str" s="37">
-        <v>採寸後に再評価</v>
-      </c>
+      <c r="A15" s="35"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="37"/>
       <c r="F15"/>
     </row>
     <row r="16">
-      <c r="A16" t="n" s="38">
-        <v>13</v>
-      </c>
-      <c r="B16" t="str" s="39">
-        <v>製品寸法</v>
-      </c>
-      <c r="C16" t="str" s="39">
-        <v>size</v>
-      </c>
-      <c r="D16" t="str" s="39">
-        <v>選択・確認</v>
-      </c>
-      <c r="E16" t="str" s="40">
-        <v>採寸後に再評価</v>
-      </c>
+      <c r="A16" s="38"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="40"/>
       <c r="F16"/>
     </row>
     <row r="17">

--- a/changes/replus-runtime-v5/candidates/RPL_ROOM.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_ROOM.xlsx
@@ -1017,7 +1017,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str" s="35">
-        <v>色連動</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B3" t="str" s="36">
         <v>sash_interior_color</v>
@@ -1032,12 +1032,12 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str" s="35">
-        <v>色連動</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B4" t="str" s="36">
         <v>exterior_cover_color</v>
@@ -1052,12 +1052,12 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str" s="35">
-        <v>色連動</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B5" t="str" s="36">
         <v>interior_cover_color</v>
@@ -1072,45 +1072,45 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str" s="35">
-        <v>フロー</v>
+        <v>NUMERIC_INPUT_PAIRS</v>
       </c>
       <c r="B6" t="str" s="36">
-        <v>window_type</v>
+        <v>dimension_basis</v>
       </c>
       <c r="C6" t="str" s="36"/>
       <c r="D6" t="str" s="36">
-        <v>{"label": "窓種", "group": "opening", "internal": false}</v>
+        <v>{"basisField": "dimension_basis", "measuredBasis": "SURVEY", "finishedBasis": "FINISHED", "legacyBasis": "FINISHED", "evaluationAssignments": {"size_mode": "CUSTOM"}, "pairs": [{"measuredField": "survey_width", "finishedField": "custom_width", "offset": -10, "message": "公式換算：仕上がり寸法 = 採寸寸法 − 10mm。"}, {"measuredField": "survey_height", "finishedField": "custom_height", "offset": -10, "message": "公式換算：仕上がり寸法 = 採寸寸法 − 10mm。"}]}</v>
       </c>
       <c r="E6" t="str" s="37">
-        <v>UI_PRESENTATION</v>
+        <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str" s="35">
-        <v>フロー</v>
+        <v>SELECTION_LINKS</v>
       </c>
       <c r="B7" t="str" s="36">
-        <v>frame_type</v>
+        <v>inner_fit_required_component</v>
       </c>
       <c r="C7" t="str" s="36">
-        <v>window_type</v>
+        <v>installation_method</v>
       </c>
       <c r="D7" t="str" s="36">
-        <v>{"label": "枠仕様", "group": "opening", "internal": false}</v>
+        <v>{"targetField": "inner_fit_required_component", "parents": ["installation_method"], "applicability": {"window_type": {"$exists": true}, "installation_method": {"$in": ["INNER_FIT_INSET", "INNER_FIT_OUTSET"]}}, "cases": [{"when": {"installation_method": "INNER_FIT_INSET"}, "value": "ROOM-UPPER-BASE"}, {"when": {"installation_method": "INNER_FIT_OUTSET"}, "value": "ROOM-UPPER-BASE"}], "resolvedMessage": "内はめ用のため必要です。数量・価格は積算で確認してください。", "pendingMessage": "内はめ仕様を選択してください。", "unavailableMessage": "必要な内はめ部材の対応を確認してください。"}</v>
       </c>
       <c r="E7" t="str" s="37">
-        <v>UI_PRESENTATION</v>
+        <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1118,19 +1118,17 @@
         <v>フロー</v>
       </c>
       <c r="B8" t="str" s="36">
-        <v>spec_panel_configuration</v>
-      </c>
-      <c r="C8" t="str" s="36">
         <v>window_type</v>
       </c>
+      <c r="C8" t="str" s="36"/>
       <c r="D8" t="str" s="36">
-        <v>{"label": "建数", "group": "opening", "internal": false}</v>
+        <v>{"label": "窓種", "group": "opening", "internal": false}</v>
       </c>
       <c r="E8" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1138,19 +1136,19 @@
         <v>フロー</v>
       </c>
       <c r="B9" t="str" s="36">
-        <v>spec_height_category</v>
+        <v>frame_type</v>
       </c>
       <c r="C9" t="str" s="36">
-        <v>window_type,custom_width,custom_height</v>
+        <v>window_type</v>
       </c>
       <c r="D9" t="str" s="36">
-        <v>{"label": "マド／テラス", "group": "opening", "internal": true}</v>
+        <v>{"label": "枠仕様", "group": "opening", "internal": false}</v>
       </c>
       <c r="E9" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1158,19 +1156,19 @@
         <v>フロー</v>
       </c>
       <c r="B10" t="str" s="36">
-        <v>spec_sash_configuration</v>
+        <v>spec_panel_configuration</v>
       </c>
       <c r="C10" t="str" s="36">
-        <v>spec_height_category,spec_panel_configuration,window_type</v>
+        <v>window_type</v>
       </c>
       <c r="D10" t="str" s="36">
-        <v>{"label": "障子仕様", "group": "opening", "internal": false}</v>
+        <v>{"label": "建数", "group": "opening", "internal": false}</v>
       </c>
       <c r="E10" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1178,19 +1176,19 @@
         <v>フロー</v>
       </c>
       <c r="B11" t="str" s="36">
-        <v>spec_opening_form</v>
+        <v>spec_height_category</v>
       </c>
       <c r="C11" t="str" s="36">
-        <v>window_type</v>
+        <v>window_type,custom_width,custom_height</v>
       </c>
       <c r="D11" t="str" s="36">
-        <v>{"label": "開口形式", "group": "opening", "internal": false}</v>
+        <v>{"label": "マド／テラス", "group": "opening", "internal": true}</v>
       </c>
       <c r="E11" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1198,19 +1196,19 @@
         <v>フロー</v>
       </c>
       <c r="B12" t="str" s="36">
-        <v>screen</v>
+        <v>spec_sash_configuration</v>
       </c>
       <c r="C12" t="str" s="36">
-        <v>spec_height_category,window_type</v>
+        <v>spec_height_category,spec_panel_configuration,window_type</v>
       </c>
       <c r="D12" t="str" s="36">
-        <v>{"label": "網戸", "group": "screen", "internal": false}</v>
+        <v>{"label": "障子仕様", "group": "opening", "internal": false}</v>
       </c>
       <c r="E12" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1218,17 +1216,19 @@
         <v>フロー</v>
       </c>
       <c r="B13" t="str" s="36">
-        <v>size_mode</v>
-      </c>
-      <c r="C13" t="str" s="36"/>
+        <v>spec_opening_form</v>
+      </c>
+      <c r="C13" t="str" s="36">
+        <v>window_type</v>
+      </c>
       <c r="D13" t="str" s="36">
-        <v>{"label": "寸法の指定方法", "group": "size", "internal": false}</v>
+        <v>{"label": "開口形式", "group": "opening", "internal": false}</v>
       </c>
       <c r="E13" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1236,19 +1236,19 @@
         <v>フロー</v>
       </c>
       <c r="B14" t="str" s="36">
-        <v>custom_width</v>
+        <v>screen</v>
       </c>
       <c r="C14" t="str" s="36">
-        <v>size_mode</v>
+        <v>spec_height_category,window_type</v>
       </c>
       <c r="D14" t="str" s="36">
-        <v>{"label": "製品仕上がり幅 W（mm）", "group": "size", "internal": false}</v>
+        <v>{"label": "網戸", "group": "screen", "internal": false}</v>
       </c>
       <c r="E14" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1256,19 +1256,17 @@
         <v>フロー</v>
       </c>
       <c r="B15" t="str" s="36">
-        <v>custom_height</v>
-      </c>
-      <c r="C15" t="str" s="36">
         <v>size_mode</v>
       </c>
+      <c r="C15" t="str" s="36"/>
       <c r="D15" t="str" s="36">
-        <v>{"label": "製品仕上がり高さ H（mm）", "group": "size", "internal": false}</v>
+        <v>{"label": "寸法の指定方法", "group": "size", "internal": true}</v>
       </c>
       <c r="E15" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1286,7 +1284,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1306,7 +1304,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1326,7 +1324,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1344,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1366,7 +1364,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1386,7 +1384,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1394,17 +1392,19 @@
         <v>フロー</v>
       </c>
       <c r="B22" t="str" s="36">
-        <v>usage_humidity</v>
-      </c>
-      <c r="C22" t="str" s="36"/>
+        <v>glass_category</v>
+      </c>
+      <c r="C22" t="str" s="36">
+        <v>window_type,frame_type</v>
+      </c>
       <c r="D22" t="str" s="36">
-        <v>{"label": "使用環境", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E22" t="str" s="37">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1412,17 +1412,19 @@
         <v>フロー</v>
       </c>
       <c r="B23" t="str" s="36">
-        <v>building_structure</v>
-      </c>
-      <c r="C23" t="str" s="36"/>
+        <v>glass</v>
+      </c>
+      <c r="C23" t="str" s="36">
+        <v>glass_category,window_type,frame_type</v>
+      </c>
       <c r="D23" t="str" s="36">
-        <v>{"label": "建物構造", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "ガラス詳細・Low-E仕様", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E23" t="str" s="37">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1430,17 +1432,19 @@
         <v>フロー</v>
       </c>
       <c r="B24" t="str" s="36">
-        <v>installation_room</v>
-      </c>
-      <c r="C24" t="str" s="36"/>
+        <v>glass_gas</v>
+      </c>
+      <c r="C24" t="str" s="36">
+        <v>frame_type,glass_category</v>
+      </c>
       <c r="D24" t="str" s="36">
-        <v>{"label": "設置場所", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "中空層", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E24" t="str" s="37">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1448,17 +1452,19 @@
         <v>フロー</v>
       </c>
       <c r="B25" t="str" s="36">
-        <v>work_space</v>
-      </c>
-      <c r="C25" t="str" s="36"/>
+        <v>glass_spacer</v>
+      </c>
+      <c r="C25" t="str" s="36">
+        <v>frame_type,glass_category,glass_gas</v>
+      </c>
       <c r="D25" t="str" s="36">
-        <v>{"label": "新設枠の振出し条件", "group": "context", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "スペーサー", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E25" t="str" s="37">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1466,19 +1472,19 @@
         <v>フロー</v>
       </c>
       <c r="B26" t="str" s="36">
-        <v>glass_category</v>
+        <v>glass_function</v>
       </c>
       <c r="C26" t="str" s="36">
-        <v>window_type,frame_type</v>
+        <v>glass_category,glass,window_type</v>
       </c>
       <c r="D26" t="str" s="36">
-        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E26" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1486,19 +1492,19 @@
         <v>フロー</v>
       </c>
       <c r="B27" t="str" s="36">
-        <v>glass</v>
+        <v>glass_appearance</v>
       </c>
       <c r="C27" t="str" s="36">
-        <v>glass_category,window_type,frame_type</v>
+        <v>glass,glass_function</v>
       </c>
       <c r="D27" t="str" s="36">
-        <v>{"label": "ガラス詳細・Low-E仕様", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
       </c>
       <c r="E27" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1506,19 +1512,17 @@
         <v>フロー</v>
       </c>
       <c r="B28" t="str" s="36">
-        <v>glass_gas</v>
-      </c>
-      <c r="C28" t="str" s="36">
-        <v>frame_type,glass_category</v>
-      </c>
+        <v>color_mode</v>
+      </c>
+      <c r="C28" t="str" s="36"/>
       <c r="D28" t="str" s="36">
-        <v>{"label": "中空層", "group": "glazing", "internal": false}</v>
+        <v>{"label": "本体の色設定", "group": "finish", "internal": false}</v>
       </c>
       <c r="E28" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -1526,19 +1530,17 @@
         <v>フロー</v>
       </c>
       <c r="B29" t="str" s="36">
-        <v>glass_spacer</v>
-      </c>
-      <c r="C29" t="str" s="36">
-        <v>frame_type,glass_category,glass_gas</v>
-      </c>
+        <v>interior_cover_type</v>
+      </c>
+      <c r="C29" t="str" s="36"/>
       <c r="D29" t="str" s="36">
-        <v>{"label": "スペーサー", "group": "glazing", "internal": false}</v>
+        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false}</v>
       </c>
       <c r="E29" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -1546,19 +1548,19 @@
         <v>フロー</v>
       </c>
       <c r="B30" t="str" s="36">
-        <v>glass_function</v>
+        <v>exterior_cover_type</v>
       </c>
       <c r="C30" t="str" s="36">
-        <v>glass_category,glass,window_type</v>
+        <v>frame_type,survey_cover_top,survey_cover_bottom,survey_cover_side</v>
       </c>
       <c r="D30" t="str" s="36">
-        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
+        <v>{"label": "化粧カバーの大きさ・組合せ", "group": "exterior_finish", "internal": false}</v>
       </c>
       <c r="E30" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -1566,19 +1568,19 @@
         <v>フロー</v>
       </c>
       <c r="B31" t="str" s="36">
-        <v>glass_appearance</v>
+        <v>installation_method</v>
       </c>
       <c r="C31" t="str" s="36">
-        <v>glass,glass_function</v>
+        <v>window_type</v>
       </c>
       <c r="D31" t="str" s="36">
-        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
+        <v>{"label": "内はめ仕様", "group": "inner_fit", "internal": false}</v>
       </c>
       <c r="E31" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -1586,17 +1588,19 @@
         <v>フロー</v>
       </c>
       <c r="B32" t="str" s="36">
-        <v>color_mode</v>
-      </c>
-      <c r="C32" t="str" s="36"/>
+        <v>inner_fit_required_component</v>
+      </c>
+      <c r="C32" t="str" s="36">
+        <v>installation_method</v>
+      </c>
       <c r="D32" t="str" s="36">
-        <v>{"label": "本体の色設定", "group": "finish", "internal": false}</v>
+        <v>{"label": "内はめ用の必須部材", "group": "inner_fit", "internal": false}</v>
       </c>
       <c r="E32" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -1604,17 +1608,17 @@
         <v>フロー</v>
       </c>
       <c r="B33" t="str" s="36">
-        <v>interior_cover_type</v>
+        <v>dimension_basis</v>
       </c>
       <c r="C33" t="str" s="36"/>
       <c r="D33" t="str" s="36">
-        <v>{"label": "室内側の仕上げ仕様", "group": "interior_finish", "internal": false}</v>
+        <v>{"label": "入力する寸法", "group": "size", "internal": false}</v>
       </c>
       <c r="E33" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="34">
@@ -1622,19 +1626,19 @@
         <v>フロー</v>
       </c>
       <c r="B34" t="str" s="36">
-        <v>exterior_cover_type</v>
+        <v>survey_width</v>
       </c>
       <c r="C34" t="str" s="36">
-        <v>frame_type,survey_cover_top,survey_cover_bottom,survey_cover_side</v>
+        <v>dimension_basis</v>
       </c>
       <c r="D34" t="str" s="36">
-        <v>{"label": "化粧カバーの大きさ・組合せ", "group": "exterior_finish", "internal": false}</v>
+        <v>{"label": "採寸幅 WS（mm）", "group": "size", "internal": false}</v>
       </c>
       <c r="E34" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F34" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="35">
@@ -1642,17 +1646,19 @@
         <v>フロー</v>
       </c>
       <c r="B35" t="str" s="36">
-        <v>survey_cover_top</v>
-      </c>
-      <c r="C35" t="str" s="36"/>
+        <v>survey_height</v>
+      </c>
+      <c r="C35" t="str" s="36">
+        <v>dimension_basis</v>
+      </c>
       <c r="D35" t="str" s="36">
-        <v>{"label": "既設上枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "採寸高さ HS（mm）", "group": "size", "internal": false}</v>
       </c>
       <c r="E35" t="str" s="37">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F35" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="36">
@@ -1660,17 +1666,19 @@
         <v>フロー</v>
       </c>
       <c r="B36" t="str" s="36">
-        <v>survey_cover_bottom</v>
-      </c>
-      <c r="C36" t="str" s="36"/>
+        <v>custom_width</v>
+      </c>
+      <c r="C36" t="str" s="36">
+        <v>dimension_basis</v>
+      </c>
       <c r="D36" t="str" s="36">
-        <v>{"label": "既設下枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "製品仕上がり幅 WD（mm）", "group": "size", "internal": false}</v>
       </c>
       <c r="E36" t="str" s="37">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F36" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
     <row r="37">
@@ -1678,17 +1686,19 @@
         <v>フロー</v>
       </c>
       <c r="B37" t="str" s="36">
-        <v>survey_cover_side</v>
-      </c>
-      <c r="C37" t="str" s="36"/>
+        <v>custom_height</v>
+      </c>
+      <c r="C37" t="str" s="36">
+        <v>dimension_basis</v>
+      </c>
       <c r="D37" t="str" s="36">
-        <v>{"label": "既設縦枠の見付（mm）", "group": "survey", "internal": false, "salesInput": false, "required": false, "externalSiteCheck": true}</v>
+        <v>{"label": "製品仕上がり高さ HD（mm）", "group": "size", "internal": false}</v>
       </c>
       <c r="E37" t="str" s="37">
-        <v>USER_APPLICATION_POLICY</v>
+        <v>UI_PRESENTATION</v>
       </c>
       <c r="F37" t="str">
-        <v>REPLUS_SALES_FLOW_V10_20261014</v>
+        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
       </c>
     </row>
   </sheetData>
@@ -1712,7 +1722,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="4" t="str">
+      <c r="A1" t="str" s="4">
         <v>90_Evidence｜根拠管理</v>
       </c>
       <c r="B1" s="4"/>
@@ -1725,7 +1735,7 @@
       <c r="I1" s="4"/>
     </row>
     <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="11" t="str">
+      <c r="A2" t="str" s="11">
         <v>確定情報は原則としてEvidence IDを持つ。URLは追跡可能なプレーンテキストで保持。</v>
       </c>
       <c r="B2" s="11"/>
@@ -1737,953 +1747,885 @@
       <c r="H2" s="11"/>
       <c r="I2" s="11"/>
     </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+      <c r="E3"/>
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="32" t="str">
+      <c r="A4" t="str" s="32">
         <v>evidence_id</v>
       </c>
-      <c r="B4" s="33" t="str">
+      <c r="B4" t="str" s="33">
         <v>情報源種別</v>
       </c>
-      <c r="C4" s="33" t="str">
+      <c r="C4" t="str" s="33">
         <v>資料名</v>
       </c>
-      <c r="D4" s="33" t="str">
+      <c r="D4" t="str" s="33">
         <v>発行年月</v>
       </c>
-      <c r="E4" s="33" t="str">
+      <c r="E4" t="str" s="33">
         <v>ページ/箇所</v>
       </c>
-      <c r="F4" s="33" t="str">
+      <c r="F4" t="str" s="33">
         <v>URL</v>
       </c>
-      <c r="G4" s="33" t="str">
+      <c r="G4" t="str" s="33">
         <v>確認日</v>
       </c>
-      <c r="H4" s="33" t="str">
+      <c r="H4" t="str" s="33">
         <v>確度</v>
       </c>
-      <c r="I4" s="34" t="str">
+      <c r="I4" t="str" s="34">
         <v>根拠内容</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="str">
+      <c r="A5" t="str" s="35">
         <v>EV-001</v>
       </c>
-      <c r="B5" s="36" t="str">
+      <c r="B5" t="str" s="36">
         <v>共通仕様</v>
       </c>
-      <c r="C5" s="36" t="str">
+      <c r="C5" t="str" s="36">
         <v>サッシ商品マスター共通仕様書_v0.1</v>
       </c>
-      <c r="D5" s="36" t="str">
+      <c r="D5" t="str" s="36">
         <v>2026-08-30更新</v>
       </c>
-      <c r="E5" s="36" t="str">
+      <c r="E5" t="str" s="36">
         <v>全体</v>
       </c>
-      <c r="F5" s="36" t="str">
+      <c r="F5" t="str" s="36">
         <v>https://docs.google.com/document/d/1MfixkbV1cZ__DtBknEKsix_nnrXQqjc-LZtXUHwJv_A/edit</v>
       </c>
-      <c r="G5" s="36" t="str">
+      <c r="G5" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H5" s="36" t="str">
+      <c r="H5" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I5" s="37" t="str">
+      <c r="I5" t="str" s="37">
         <v>共通階層・条件判定・Evidence・UI非表示ルール</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="str">
+      <c r="A6" t="str" s="35">
         <v>EV-002</v>
       </c>
-      <c r="B6" s="36" t="str">
+      <c r="B6" t="str" s="36">
         <v>業務用資料集</v>
       </c>
-      <c r="C6" s="36" t="str">
+      <c r="C6" t="str" s="36">
         <v>リプラス・リプラスマンション用 取替窓 業務用資料集</v>
       </c>
-      <c r="D6" s="36" t="str">
+      <c r="D6" t="str" s="36">
         <v>2026-04</v>
       </c>
-      <c r="E6" s="36" t="str">
+      <c r="E6" t="str" s="36">
         <v>目次・居室仕様価格表/納まり</v>
       </c>
-      <c r="F6" s="36" t="str">
+      <c r="F6" t="str" s="36">
         <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
       </c>
-      <c r="G6" s="36" t="str">
+      <c r="G6" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H6" s="36" t="str">
+      <c r="H6" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I6" s="37" t="str">
+      <c r="I6" t="str" s="37">
         <v>現行業務用資料。居室仕様の窓種、標準枠/ブリッジ枠、価格表・納まり</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="str">
+      <c r="A7" t="str" s="35">
         <v>EV-003</v>
       </c>
-      <c r="B7" s="36" t="str">
+      <c r="B7" t="str" s="36">
         <v>商品カタログ</v>
       </c>
-      <c r="C7" s="36" t="str">
+      <c r="C7" t="str" s="36">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D7" s="36" t="str">
+      <c r="D7" t="str" s="36">
         <v>2025-08</v>
       </c>
-      <c r="E7" s="36" t="str">
+      <c r="E7" t="str" s="36">
         <v>p.28</v>
       </c>
-      <c r="F7" s="36" t="str">
+      <c r="F7" t="str" s="36">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G7" s="36" t="str">
+      <c r="G7" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H7" s="36" t="str">
+      <c r="H7" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I7" s="37" t="str">
+      <c r="I7" t="str" s="37">
         <v>居室仕様の8窓種、色体系、既設窓取替可否の基本説明</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="str">
+      <c r="A8" t="str" s="35">
         <v>EV-004</v>
       </c>
-      <c r="B8" s="36" t="str">
+      <c r="B8" t="str" s="36">
         <v>商品カタログ</v>
       </c>
-      <c r="C8" s="36" t="str">
+      <c r="C8" t="str" s="36">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D8" s="36" t="str">
+      <c r="D8" t="str" s="36">
         <v>2025-08</v>
       </c>
-      <c r="E8" s="36" t="str">
+      <c r="E8" t="str" s="36">
         <v>p.48～</v>
       </c>
-      <c r="F8" s="36" t="str">
+      <c r="F8" t="str" s="36">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G8" s="36" t="str">
+      <c r="G8" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H8" s="36" t="str">
+      <c r="H8" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I8" s="37" t="str">
+      <c r="I8" t="str" s="37">
         <v>ガラスバリエーション</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="str">
+      <c r="A9" t="str" s="35">
         <v>EV-005</v>
       </c>
-      <c r="B9" s="36" t="str">
+      <c r="B9" t="str" s="36">
         <v>商品カタログ</v>
       </c>
-      <c r="C9" s="36" t="str">
+      <c r="C9" t="str" s="36">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D9" s="36" t="str">
+      <c r="D9" t="str" s="36">
         <v>2025-08</v>
       </c>
-      <c r="E9" s="36" t="str">
+      <c r="E9" t="str" s="36">
         <v>p.64-65</v>
       </c>
-      <c r="F9" s="36" t="str">
+      <c r="F9" t="str" s="36">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G9" s="36" t="str">
+      <c r="G9" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H9" s="36" t="str">
+      <c r="H9" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I9" s="37" t="str">
+      <c r="I9" t="str" s="37">
         <v>網戸形式・機能性ネット・シリーズ設定表</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="str">
+      <c r="A10" t="str" s="35">
         <v>EV-006</v>
       </c>
-      <c r="B10" s="36" t="str">
+      <c r="B10" t="str" s="36">
         <v>商品カタログ</v>
       </c>
-      <c r="C10" s="36" t="str">
+      <c r="C10" t="str" s="36">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D10" s="36" t="str">
+      <c r="D10" t="str" s="36">
         <v>2025-08</v>
       </c>
-      <c r="E10" s="36" t="str">
+      <c r="E10" t="str" s="36">
         <v>p.97</v>
       </c>
-      <c r="F10" s="36" t="str">
+      <c r="F10" t="str" s="36">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G10" s="36" t="str">
+      <c r="G10" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H10" s="36" t="str">
+      <c r="H10" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I10" s="37" t="str">
+      <c r="I10" t="str" s="37">
         <v>居室仕様 引違い窓 標準枠 寸法特注範囲</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="str">
+      <c r="A11" t="str" s="35">
         <v>EV-007</v>
       </c>
-      <c r="B11" s="36" t="str">
+      <c r="B11" t="str" s="36">
         <v>商品カタログ</v>
       </c>
-      <c r="C11" s="36" t="str">
+      <c r="C11" t="str" s="36">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D11" s="36" t="str">
+      <c r="D11" t="str" s="36">
         <v>2025-08</v>
       </c>
-      <c r="E11" s="36" t="str">
+      <c r="E11" t="str" s="36">
         <v>p.98</v>
       </c>
-      <c r="F11" s="36" t="str">
+      <c r="F11" t="str" s="36">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G11" s="36" t="str">
+      <c r="G11" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H11" s="36" t="str">
+      <c r="H11" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I11" s="37" t="str">
+      <c r="I11" t="str" s="37">
         <v>居室仕様 引違い窓 ブリッジ枠 寸法特注範囲</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="str">
+      <c r="A12" t="str" s="35">
         <v>EV-008</v>
       </c>
-      <c r="B12" s="36" t="str">
+      <c r="B12" t="str" s="36">
         <v>商品カタログ</v>
       </c>
-      <c r="C12" s="36" t="str">
+      <c r="C12" t="str" s="36">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D12" s="36" t="str">
+      <c r="D12" t="str" s="36">
         <v>2025-08</v>
       </c>
-      <c r="E12" s="36" t="str">
+      <c r="E12" t="str" s="36">
         <v>p.110</v>
       </c>
-      <c r="F12" s="36" t="str">
+      <c r="F12" t="str" s="36">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G12" s="36" t="str">
+      <c r="G12" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H12" s="36" t="str">
+      <c r="H12" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I12" s="37" t="str">
+      <c r="I12" t="str" s="37">
         <v>居室仕様 装飾窓 寸法特注範囲</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="str">
+      <c r="A13" t="str" s="35">
         <v>EV-009</v>
       </c>
-      <c r="B13" s="36" t="str">
+      <c r="B13" t="str" s="36">
         <v>商品カタログ</v>
       </c>
-      <c r="C13" s="36" t="str">
+      <c r="C13" t="str" s="36">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D13" s="36" t="str">
+      <c r="D13" t="str" s="36">
         <v>2025-08</v>
       </c>
-      <c r="E13" s="36" t="str">
+      <c r="E13" t="str" s="36">
         <v>p.111</v>
       </c>
-      <c r="F13" s="36" t="str">
+      <c r="F13" t="str" s="36">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G13" s="36" t="str">
+      <c r="G13" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H13" s="36" t="str">
+      <c r="H13" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I13" s="37" t="str">
+      <c r="I13" t="str" s="37">
         <v>FIX窓、連窓方立、段窓無目 寸法特注範囲</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="str">
+      <c r="A14" t="str" s="35">
         <v>EV-010</v>
       </c>
-      <c r="B14" s="36" t="str">
+      <c r="B14" t="str" s="36">
         <v>商品カタログ</v>
       </c>
-      <c r="C14" s="36" t="str">
+      <c r="C14" t="str" s="36">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D14" s="36" t="str">
+      <c r="D14" t="str" s="36">
         <v>2025-08</v>
       </c>
-      <c r="E14" s="36" t="str">
+      <c r="E14" t="str" s="36">
         <v>p.194-200</v>
       </c>
-      <c r="F14" s="36" t="str">
+      <c r="F14" t="str" s="36">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G14" s="36" t="str">
+      <c r="G14" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H14" s="36" t="str">
+      <c r="H14" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I14" s="37" t="str">
+      <c r="I14" t="str" s="37">
         <v>現場調査フロー、構造/防火/既設サッシ条件</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="str">
+      <c r="A15" t="str" s="35">
         <v>EV-011</v>
       </c>
-      <c r="B15" s="36" t="str">
+      <c r="B15" t="str" s="36">
         <v>商品カタログ</v>
       </c>
-      <c r="C15" s="36" t="str">
+      <c r="C15" t="str" s="36">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D15" s="36" t="str">
+      <c r="D15" t="str" s="36">
         <v>2025-08</v>
       </c>
-      <c r="E15" s="36" t="str">
+      <c r="E15" t="str" s="36">
         <v>p.200</v>
       </c>
-      <c r="F15" s="36" t="str">
+      <c r="F15" t="str" s="36">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G15" s="36" t="str">
+      <c r="G15" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H15" s="36" t="str">
+      <c r="H15" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I15" s="37" t="str">
+      <c r="I15" t="str" s="37">
         <v>既設窓種対応可否表</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="str">
+      <c r="A16" t="str" s="35">
         <v>EV-012</v>
       </c>
-      <c r="B16" s="36" t="str">
+      <c r="B16" t="str" s="36">
         <v>商品カタログ</v>
       </c>
-      <c r="C16" s="36" t="str">
+      <c r="C16" t="str" s="36">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D16" s="36" t="str">
+      <c r="D16" t="str" s="36">
         <v>2025-08</v>
       </c>
-      <c r="E16" s="36" t="str">
+      <c r="E16" t="str" s="36">
         <v>p.204-209付近</v>
       </c>
-      <c r="F16" s="36" t="str">
+      <c r="F16" t="str" s="36">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G16" s="36" t="str">
+      <c r="G16" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H16" s="36" t="str">
+      <c r="H16" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I16" s="37" t="str">
+      <c r="I16" t="str" s="37">
         <v>採寸・下枠補強金具・枠見付確認</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="str">
+      <c r="A17" t="str" s="35">
         <v>EV-013</v>
       </c>
-      <c r="B17" s="36" t="str">
+      <c r="B17" t="str" s="36">
         <v>商品カタログ</v>
       </c>
-      <c r="C17" s="36" t="str">
+      <c r="C17" t="str" s="36">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D17" s="36" t="str">
+      <c r="D17" t="str" s="36">
         <v>2025-08</v>
       </c>
-      <c r="E17" s="36" t="str">
+      <c r="E17" t="str" s="36">
         <v>納まり参考図 p.152以降</v>
       </c>
-      <c r="F17" s="36" t="str">
+      <c r="F17" t="str" s="36">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G17" s="36" t="str">
+      <c r="G17" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H17" s="36" t="str">
+      <c r="H17" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I17" s="37" t="str">
+      <c r="I17" t="str" s="37">
         <v>出来寸W=WS-10、出来寸H=HS-10の寸法表記</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="str">
+      <c r="A18" t="str" s="35">
         <v>EV-014</v>
       </c>
-      <c r="B18" s="36" t="str">
+      <c r="B18" t="str" s="36">
         <v>公式Web</v>
       </c>
-      <c r="C18" s="36" t="str">
+      <c r="C18" t="str" s="36">
         <v>LIXIL リプラス 居室仕様</v>
       </c>
-      <c r="D18" s="36" t="str">
+      <c r="D18" t="str" s="36">
         <v>現行</v>
       </c>
-      <c r="E18" s="36" t="str">
+      <c r="E18" t="str" s="36">
         <v>ブリッジ枠・色・ガラス・網戸</v>
       </c>
-      <c r="F18" s="36" t="str">
+      <c r="F18" t="str" s="36">
         <v>https://www.lixil.co.jp/lineup/window/replus/variation/dedicated-frame/</v>
       </c>
-      <c r="G18" s="36" t="str">
+      <c r="G18" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H18" s="36" t="str">
+      <c r="H18" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I18" s="37" t="str">
+      <c r="I18" t="str" s="37">
         <v>ブリッジ枠は引違い窓で選択可。色/ガラス/網戸の現行掲載</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="str">
+      <c r="A19" t="str" s="35">
         <v>EV-015</v>
       </c>
-      <c r="B19" s="36" t="str">
+      <c r="B19" t="str" s="36">
         <v>公式Webカタログ</v>
       </c>
-      <c r="C19" s="36" t="str">
+      <c r="C19" t="str" s="36">
         <v>リプラス・リプラスマンション用 業務用資料集 IS8000</v>
       </c>
-      <c r="D19" s="36" t="str">
+      <c r="D19" t="str" s="36">
         <v>2026-04</v>
       </c>
-      <c r="E19" s="36" t="str">
+      <c r="E19" t="str" s="36">
         <v>244ページ</v>
       </c>
-      <c r="F19" s="36" t="str">
+      <c r="F19" t="str" s="36">
         <v>https://webcatalog.lixil.co.jp/iportal/CatalogDetail.do?catalogID=18008840000&amp;categoryID=1680000&amp;designID=newinter&amp;method=initial_screen&amp;position=25&amp;type=mc&amp;volumeID=LXL13001</v>
       </c>
-      <c r="G19" s="36" t="str">
+      <c r="G19" t="str" s="36">
         <v>2026-08-30</v>
       </c>
-      <c r="H19" s="36" t="str">
+      <c r="H19" t="str" s="36">
         <v>HIGH</v>
       </c>
-      <c r="I19" s="37" t="str">
+      <c r="I19" t="str" s="37">
         <v>現行業務用資料の発行年月確認</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="38" t="str">
+      <c r="A20" t="str" s="38">
         <v>EV-016</v>
       </c>
-      <c r="B20" s="39" t="str">
+      <c r="B20" t="str" s="39">
         <v>LIXIL KIN-KEN</v>
       </c>
-      <c r="C20" s="39" t="str">
+      <c r="C20" t="str" s="39">
         <v>リプラス 商品資料一覧</v>
       </c>
-      <c r="D20" s="39" t="str">
+      <c r="D20" t="str" s="39">
         <v>現行</v>
       </c>
-      <c r="E20" s="39" t="str">
+      <c r="E20" t="str" s="39">
         <v>商品資料</v>
       </c>
-      <c r="F20" s="39" t="str">
+      <c r="F20" t="str" s="39">
         <v>https://kinken.lixil.co.jp/e/products/csseresdet_2671800/documents/webcatalog</v>
       </c>
-      <c r="G20" s="39" t="str">
+      <c r="G20" t="str" s="39">
         <v>2026-08-30</v>
       </c>
-      <c r="H20" s="39" t="str">
+      <c r="H20" t="str" s="39">
         <v>HIGH</v>
       </c>
-      <c r="I20" s="40" t="str">
+      <c r="I20" t="str" s="40">
         <v>現行資料コード/発行時期の確認</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="str">
+      <c r="A21" t="str" s="28">
         <v>EV-017</v>
       </c>
-      <c r="B21" s="28" t="str">
+      <c r="B21" t="str" s="28">
         <v>商品カタログ</v>
       </c>
-      <c r="C21" s="28" t="str">
+      <c r="C21" t="str" s="28">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D21" s="28" t="str">
+      <c r="D21" t="str" s="28">
         <v>2025-08</v>
       </c>
-      <c r="E21" s="28" t="str">
+      <c r="E21" t="str" s="28">
         <v>p.64-65 / p.69</v>
       </c>
-      <c r="F21" s="28" t="str">
+      <c r="F21" t="str" s="28">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G21" s="28" t="str">
+      <c r="G21" t="str" s="28">
         <v>2026-08-30</v>
       </c>
-      <c r="H21" s="28" t="str">
+      <c r="H21" t="str" s="28">
         <v>HIGH</v>
       </c>
-      <c r="I21" s="28" t="str">
+      <c r="I21" t="str" s="28">
         <v>居室仕様の網戸形式・機能性ネット・新設サッシ別代表網戸</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="str">
+      <c r="A22" t="str" s="28">
         <v>EV-018</v>
       </c>
-      <c r="B22" s="28" t="str">
+      <c r="B22" t="str" s="28">
         <v>商品カタログ</v>
       </c>
-      <c r="C22" s="28" t="str">
+      <c r="C22" t="str" s="28">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D22" s="28" t="str">
+      <c r="D22" t="str" s="28">
         <v>2025-08</v>
       </c>
-      <c r="E22" s="28" t="str">
+      <c r="E22" t="str" s="28">
         <v>p.124</v>
       </c>
-      <c r="F22" s="28" t="str">
+      <c r="F22" t="str" s="28">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G22" s="28" t="str">
+      <c r="G22" t="str" s="28">
         <v>2026-08-30</v>
       </c>
-      <c r="H22" s="28" t="str">
+      <c r="H22" t="str" s="28">
         <v>HIGH</v>
       </c>
-      <c r="I22" s="28" t="str">
+      <c r="I22" t="str" s="28">
         <v>有償品取付可否表・注記1～16</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="str">
+      <c r="A23" t="str" s="28">
         <v>EV-019</v>
       </c>
-      <c r="B23" s="28" t="str">
+      <c r="B23" t="str" s="28">
         <v>商品カタログ</v>
       </c>
-      <c r="C23" s="28" t="str">
+      <c r="C23" t="str" s="28">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D23" s="28" t="str">
+      <c r="D23" t="str" s="28">
         <v>2025-08</v>
       </c>
-      <c r="E23" s="28" t="str">
+      <c r="E23" t="str" s="28">
         <v>p.208-211</v>
       </c>
-      <c r="F23" s="28" t="str">
+      <c r="F23" t="str" s="28">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G23" s="28" t="str">
+      <c r="G23" t="str" s="28">
         <v>2026-08-30</v>
       </c>
-      <c r="H23" s="28" t="str">
+      <c r="H23" t="str" s="28">
         <v>HIGH</v>
       </c>
-      <c r="I23" s="28" t="str">
+      <c r="I23" t="str" s="28">
         <v>標準施工/内嵌め判定・下枠補強金具・3点採寸・化粧カバー見付範囲</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="str">
+      <c r="A24" t="str" s="28">
         <v>EV-020</v>
       </c>
-      <c r="B24" s="28" t="str">
+      <c r="B24" t="str" s="28">
         <v>商品カタログ</v>
       </c>
-      <c r="C24" s="28" t="str">
+      <c r="C24" t="str" s="28">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D24" s="28" t="str">
+      <c r="D24" t="str" s="28">
         <v>2025-08</v>
       </c>
-      <c r="E24" s="28" t="str">
+      <c r="E24" t="str" s="28">
         <v>p.48-49</v>
       </c>
-      <c r="F24" s="28" t="str">
+      <c r="F24" t="str" s="28">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G24" s="28" t="str">
+      <c r="G24" t="str" s="28">
         <v>2026-08-30</v>
       </c>
-      <c r="H24" s="28" t="str">
+      <c r="H24" t="str" s="28">
         <v>HIGH</v>
       </c>
-      <c r="I24" s="28" t="str">
+      <c r="I24" t="str" s="28">
         <v>居室仕様の複層ガラス体系・Low-E・中空層・追加機能</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="str">
+      <c r="A25" t="str" s="28">
         <v>EV-021</v>
       </c>
-      <c r="B25" s="28" t="str">
+      <c r="B25" t="str" s="28">
         <v>商品カタログ</v>
       </c>
-      <c r="C25" s="28" t="str">
+      <c r="C25" t="str" s="28">
         <v>LIXIL リプラス 商品カタログ SN1200</v>
       </c>
-      <c r="D25" s="28" t="str">
+      <c r="D25" t="str" s="28">
         <v>2025-08</v>
       </c>
-      <c r="E25" s="28" t="str">
+      <c r="E25" t="str" s="28">
         <v>p.76</v>
       </c>
-      <c r="F25" s="28" t="str">
+      <c r="F25" t="str" s="28">
         <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
       </c>
-      <c r="G25" s="28" t="str">
+      <c r="G25" t="str" s="28">
         <v>2026-08-30</v>
       </c>
-      <c r="H25" s="28" t="str">
+      <c r="H25" t="str" s="28">
         <v>HIGH</v>
       </c>
-      <c r="I25" s="28" t="str">
+      <c r="I25" t="str" s="28">
         <v>見込みふかし部材の適用条件</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="str">
+      <c r="A26" t="str" s="28">
         <v>EV-022</v>
       </c>
-      <c r="B26" s="28" t="str">
+      <c r="B26" t="str" s="28">
         <v>業務用資料集</v>
       </c>
-      <c r="C26" s="28" t="str">
+      <c r="C26" t="str" s="28">
         <v>リプラス・リプラスマンション用 取替窓 業務用資料集</v>
       </c>
-      <c r="D26" s="28" t="str">
+      <c r="D26" t="str" s="28">
         <v>2026-04</v>
       </c>
-      <c r="E26" s="28" t="str">
+      <c r="E26" t="str" s="28">
         <v>居室仕様完成品価格表・有償品</v>
       </c>
-      <c r="F26" s="28" t="str">
+      <c r="F26" t="str" s="28">
         <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
       </c>
-      <c r="G26" s="28" t="str">
+      <c r="G26" t="str" s="28">
         <v>2026-08-30</v>
       </c>
-      <c r="H26" s="28" t="str">
+      <c r="H26" t="str" s="28">
         <v>HIGH</v>
       </c>
-      <c r="I26" s="28" t="str">
+      <c r="I26" t="str" s="28">
         <v>中桟有無・有償品・価格区分の現行確認</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>DELTA-KEY-EV-V4</t>
-        </is>
-      </c>
-      <c r="B27" s="28" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C27" s="28" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D27" s="28" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E27" s="28" t="inlineStr">
-        <is>
-          <t>PDF 3,44,49</t>
-        </is>
-      </c>
-      <c r="F27" s="28" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G27" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H27" s="28" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I27" s="28" t="inlineStr">
-        <is>
-          <t>ADD_OPTION_AND_DENY_COMBINATION / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A27" t="str" s="28">
+        <v>DELTA-KEY-EV-V4</v>
+      </c>
+      <c r="B27" t="str" s="28">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C27" t="str" s="28">
+        <v>IS9800</v>
+      </c>
+      <c r="D27" t="str" s="28">
+        <v>2026-10</v>
+      </c>
+      <c r="E27" t="str" s="28">
+        <v>PDF 3,44,49</v>
+      </c>
+      <c r="F27" t="str" s="28">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G27" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H27" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I27" t="str" s="28">
+        <v>ADD_OPTION_AND_DENY_COMBINATION / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="inlineStr">
-        <is>
-          <t>DELTA-SPACER-EV-V4</t>
-        </is>
-      </c>
-      <c r="B28" s="28" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C28" s="28" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D28" s="28" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E28" s="28" t="inlineStr">
-        <is>
-          <t>PDF 52,104,116,120</t>
-        </is>
-      </c>
-      <c r="F28" s="28" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G28" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H28" s="28" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I28" s="28" t="inlineStr">
-        <is>
-          <t>ADD_15x20_SPACER / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A28" t="str" s="28">
+        <v>DELTA-SPACER-EV-V4</v>
+      </c>
+      <c r="B28" t="str" s="28">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C28" t="str" s="28">
+        <v>IS9800</v>
+      </c>
+      <c r="D28" t="str" s="28">
+        <v>2026-10</v>
+      </c>
+      <c r="E28" t="str" s="28">
+        <v>PDF 52,104,116,120</v>
+      </c>
+      <c r="F28" t="str" s="28">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G28" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H28" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I28" t="str" s="28">
+        <v>ADD_15x20_SPACER / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>DELTA-CASING-EV-V4</t>
-        </is>
-      </c>
-      <c r="B29" s="28" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C29" s="28" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D29" s="28" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E29" s="28" t="inlineStr">
-        <is>
-          <t>PDF 51,115,119</t>
-        </is>
-      </c>
-      <c r="F29" s="28" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G29" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H29" s="28" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I29" s="28" t="inlineStr">
-        <is>
-          <t>UPDATE_WOODEN_CASING_COLOR_SCOPE / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A29" t="str" s="28">
+        <v>DELTA-CASING-EV-V4</v>
+      </c>
+      <c r="B29" t="str" s="28">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C29" t="str" s="28">
+        <v>IS9800</v>
+      </c>
+      <c r="D29" t="str" s="28">
+        <v>2026-10</v>
+      </c>
+      <c r="E29" t="str" s="28">
+        <v>PDF 51,115,119</v>
+      </c>
+      <c r="F29" t="str" s="28">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G29" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H29" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I29" t="str" s="28">
+        <v>UPDATE_WOODEN_CASING_COLOR_SCOPE / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="inlineStr">
-        <is>
-          <t>DELTA-FILLER-EV-V4</t>
-        </is>
-      </c>
-      <c r="B30" s="28" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C30" s="28" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D30" s="28" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E30" s="28" t="inlineStr">
-        <is>
-          <t>PDF 51,115,119</t>
-        </is>
-      </c>
-      <c r="F30" s="28" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G30" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H30" s="28" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I30" s="28" t="inlineStr">
-        <is>
-          <t>UPDATE_FILLER_NAME_AND_VARIANTS / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A30" t="str" s="28">
+        <v>DELTA-FILLER-EV-V4</v>
+      </c>
+      <c r="B30" t="str" s="28">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C30" t="str" s="28">
+        <v>IS9800</v>
+      </c>
+      <c r="D30" t="str" s="28">
+        <v>2026-10</v>
+      </c>
+      <c r="E30" t="str" s="28">
+        <v>PDF 51,115,119</v>
+      </c>
+      <c r="F30" t="str" s="28">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G30" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H30" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I30" t="str" s="28">
+        <v>UPDATE_FILLER_NAME_AND_VARIANTS / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>DELTA-LEADTIME-EV-V4</t>
-        </is>
-      </c>
-      <c r="B31" s="28" t="inlineStr">
-        <is>
-          <t>公式業務用資料集</t>
-        </is>
-      </c>
-      <c r="C31" s="28" t="inlineStr">
-        <is>
-          <t>IS9800</t>
-        </is>
-      </c>
-      <c r="D31" s="28" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="E31" s="28" t="inlineStr">
-        <is>
-          <t>PDF 235</t>
-        </is>
-      </c>
-      <c r="F31" s="28" t="inlineStr">
-        <is>
-          <t>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</t>
-        </is>
-      </c>
-      <c r="G31" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H31" s="28" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I31" s="28" t="inlineStr">
-        <is>
-          <t>SOURCE_NOTE_ONLY / NEW_CANDIDATE、Current未採用</t>
-        </is>
+      <c r="A31" t="str" s="28">
+        <v>DELTA-LEADTIME-EV-V4</v>
+      </c>
+      <c r="B31" t="str" s="28">
+        <v>公式業務用資料集</v>
+      </c>
+      <c r="C31" t="str" s="28">
+        <v>IS9800</v>
+      </c>
+      <c r="D31" t="str" s="28">
+        <v>2026-10</v>
+      </c>
+      <c r="E31" t="str" s="28">
+        <v>PDF 235</v>
+      </c>
+      <c r="F31" t="str" s="28">
+        <v>https://webcatalog.lixil.co.jp/cgi-bin/openCatalog.cgi?c=IS9800&amp;d=newinter</v>
+      </c>
+      <c r="G31" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H31" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I31" t="str" s="28">
+        <v>SOURCE_NOTE_ONLY / NEW_CANDIDATE、Current未採用</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>EV-V5-CASING</t>
-        </is>
-      </c>
-      <c r="B32" s="28" t="inlineStr">
-        <is>
-          <t>業務用資料集</t>
-        </is>
-      </c>
-      <c r="C32" s="28" t="inlineStr">
-        <is>
-          <t>IS8000</t>
-        </is>
-      </c>
-      <c r="D32" s="28" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="E32" s="28" t="inlineStr">
-        <is>
-          <t>PDF51 印刷49</t>
-        </is>
-      </c>
-      <c r="F32" s="28" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</t>
-        </is>
-      </c>
-      <c r="G32" s="28" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="H32" s="28" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="I32" s="28" t="inlineStr">
-        <is>
-          <t>既存カバー用ケーシングの選択ID補完。価格/BOM/SetCode未確定</t>
-        </is>
+      <c r="A32" t="str" s="28">
+        <v>EV-V5-CASING</v>
+      </c>
+      <c r="B32" t="str" s="28">
+        <v>業務用資料集</v>
+      </c>
+      <c r="C32" t="str" s="28">
+        <v>IS8000</v>
+      </c>
+      <c r="D32" t="str" s="28">
+        <v>2026-04</v>
+      </c>
+      <c r="E32" t="str" s="28">
+        <v>PDF51 印刷49</v>
+      </c>
+      <c r="F32" t="str" s="28">
+        <v>https://drive.google.com/file/d/1D1HPMXhOMYd_Lu10XNzzJR2TH3aDHVUr/view</v>
+      </c>
+      <c r="G32" t="str" s="28">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H32" t="str" s="28">
+        <v>HIGH</v>
+      </c>
+      <c r="I32" t="str" s="28">
+        <v>既存カバー用ケーシングの選択ID補完。価格/BOM/SetCode未確定</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>EV-DIMENSIONS-INNER-FIT-V11</v>
+      </c>
+      <c r="B33" t="str">
+        <v>公式商品カタログ</v>
+      </c>
+      <c r="C33" t="str">
+        <v>リプラス SN1200</v>
+      </c>
+      <c r="D33" t="str">
+        <v>2025-08</v>
+      </c>
+      <c r="E33" t="str">
+        <v>PDF252/254・231/233/247/249/251</v>
+      </c>
+      <c r="F33" t="str">
+        <v>https://drive.google.com/file/d/1wH1nhmsftl6y8Mp7y6twtoXSi6rxqxzT/view</v>
+      </c>
+      <c r="G33" t="str">
+        <v>2026-10-14</v>
+      </c>
+      <c r="H33" t="str">
+        <v>HIGH</v>
+      </c>
+      <c r="I33" t="str">
+        <v>採寸/出来寸の相互換算と標準/内はめの施工仕様を共通Runtimeへ接続</v>
       </c>
     </row>
   </sheetData>
@@ -11603,7 +11545,7 @@
         <v>リプラス住宅用 → 仕様</v>
       </c>
       <c r="E4" t="str" s="37">
-        <v>今回承認されたアプリ運用ルール</v>
+        <v>アプリ運用ルール</v>
       </c>
       <c r="F4"/>
     </row>
@@ -11684,16 +11626,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="str" s="36">
-        <v>室内側の仕上げ・アングルカバー</v>
+        <v>内はめ仕様</v>
       </c>
       <c r="C9" t="str" s="36">
-        <v>interior_finish</v>
+        <v>inner_fit</v>
       </c>
       <c r="D9" t="str" s="36">
         <v>選択・確認</v>
       </c>
       <c r="E9" t="str" s="37">
-        <v>本体色に連動</v>
+        <v>ガラスの後で選択</v>
       </c>
       <c r="F9"/>
     </row>
@@ -11702,16 +11644,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="str" s="36">
-        <v>室外側の仕上げ・化粧カバー</v>
+        <v>室内側の仕上げ・アングルカバー</v>
       </c>
       <c r="C10" t="str" s="36">
-        <v>exterior_finish</v>
+        <v>interior_finish</v>
       </c>
       <c r="D10" t="str" s="36">
         <v>選択・確認</v>
       </c>
       <c r="E10" t="str" s="37">
-        <v>本体色に連動</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F10"/>
     </row>
@@ -11720,10 +11662,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="str" s="36">
-        <v>追加部材・オプション</v>
+        <v>室外側の仕上げ・化粧カバー</v>
       </c>
       <c r="C11" t="str" s="36">
-        <v>options</v>
+        <v>exterior_finish</v>
       </c>
       <c r="D11" t="str" s="36">
         <v>選択・確認</v>
@@ -11738,10 +11680,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="str" s="36">
-        <v>選択した部材の仕様</v>
+        <v>追加部材・オプション</v>
       </c>
       <c r="C12" t="str" s="36">
-        <v>part_detail</v>
+        <v>options</v>
       </c>
       <c r="D12" t="str" s="36">
         <v>選択・確認</v>
@@ -11756,25 +11698,35 @@
         <v>10</v>
       </c>
       <c r="B13" t="str" s="36">
-        <v>製品寸法</v>
+        <v>選択した部材の仕様</v>
       </c>
       <c r="C13" t="str" s="36">
-        <v>size</v>
+        <v>part_detail</v>
       </c>
       <c r="D13" t="str" s="36">
         <v>選択・確認</v>
       </c>
       <c r="E13" t="str" s="37">
-        <v>採寸後に再評価</v>
+        <v>対応する項目のみ表示</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14">
-      <c r="A14" s="35"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="37"/>
+      <c r="A14" t="n" s="35">
+        <v>11</v>
+      </c>
+      <c r="B14" t="str" s="36">
+        <v>製品寸法</v>
+      </c>
+      <c r="C14" t="str" s="36">
+        <v>size</v>
+      </c>
+      <c r="D14" t="str" s="36">
+        <v>選択・確認</v>
+      </c>
+      <c r="E14" t="str" s="37">
+        <v>採寸と仕上がりを併記</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15">

--- a/changes/replus-runtime-v5/candidates/RPL_ROOM.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_ROOM.xlsx
@@ -1032,7 +1032,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1052,7 +1052,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1072,7 +1072,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1090,7 +1090,7 @@
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1104,13 +1104,13 @@
         <v>installation_method</v>
       </c>
       <c r="D7" t="str" s="36">
-        <v>{"targetField": "inner_fit_required_component", "parents": ["installation_method"], "applicability": {"window_type": {"$exists": true}, "installation_method": {"$in": ["INNER_FIT_INSET", "INNER_FIT_OUTSET"]}}, "cases": [{"when": {"installation_method": "INNER_FIT_INSET"}, "value": "ROOM-UPPER-BASE"}, {"when": {"installation_method": "INNER_FIT_OUTSET"}, "value": "ROOM-UPPER-BASE"}], "resolvedMessage": "内はめ用のため必要です。数量・価格は積算で確認してください。", "pendingMessage": "内はめ仕様を選択してください。", "unavailableMessage": "必要な内はめ部材の対応を確認してください。"}</v>
+        <v>{"targetField": "inner_fit_required_component", "parents": ["installation_method"], "applicability": {"window_type": {"$exists": true}, "installation_method": {"$in": ["INNER_FIT_INSET", "INNER_FIT_OUTSET"]}}, "cases": [{"when": {"installation_method": "INNER_FIT_INSET"}, "value": "ROOM-UPPER-BASE"}, {"when": {"installation_method": "INNER_FIT_OUTSET"}, "value": "ROOM-UPPER-BASE"}], "resolvedMessage": "内はめ用のため必要です。数量・価格は積算で確認してください。", "pendingMessage": "内はめ仕様を選択してください。", "unavailableMessage": "必要な内はめ部材の対応を確認してください。", "resolvedNoticeVisibility": "INTERNAL_ONLY"}</v>
       </c>
       <c r="E7" t="str" s="37">
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1128,7 +1128,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1148,7 +1148,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1168,7 +1168,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1188,7 +1188,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1208,7 +1208,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1228,7 +1228,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1248,7 +1248,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1266,7 +1266,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1284,7 +1284,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1318,13 +1318,13 @@
         <v>sash_exterior_color</v>
       </c>
       <c r="D18" t="str" s="36">
-        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": false}</v>
+        <v>{"label": "化粧カバー色（外観色に連動）", "group": "exterior_finish", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E18" t="str" s="37">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1338,13 +1338,13 @@
         <v>sash_interior_color</v>
       </c>
       <c r="D19" t="str" s="36">
-        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": false}</v>
+        <v>{"label": "室内カバー色（内観色に連動）", "group": "interior_finish", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E19" t="str" s="37">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1364,7 +1364,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1384,7 +1384,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1404,7 +1404,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1424,7 +1424,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1444,7 +1444,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1464,7 +1464,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1484,7 +1484,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1504,7 +1504,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1522,7 +1522,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -1540,7 +1540,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -1560,7 +1560,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -1580,7 +1580,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -1594,13 +1594,13 @@
         <v>installation_method</v>
       </c>
       <c r="D32" t="str" s="36">
-        <v>{"label": "内はめ用の必須部材", "group": "inner_fit", "internal": false}</v>
+        <v>{"label": "内はめ用の必須部材", "group": "inner_fit", "internal": true, "salesDisplay": false}</v>
       </c>
       <c r="E32" t="str" s="37">
-        <v>UI_PRESENTATION</v>
+        <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -1618,7 +1618,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="34">
@@ -1638,7 +1638,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F34" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="35">
@@ -1658,7 +1658,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F35" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="36">
@@ -1678,7 +1678,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F36" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F37" t="str">
-        <v>REPLUS_DIMENSIONS_INNER_FIT_V11_20261014</v>
+        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
       </c>
     </row>
   </sheetData>

--- a/changes/replus-runtime-v5/candidates/RPL_ROOM.xlsx
+++ b/changes/replus-runtime-v5/candidates/RPL_ROOM.xlsx
@@ -1032,7 +1032,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F3" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="4">
@@ -1052,7 +1052,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F4" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="5">
@@ -1072,7 +1072,7 @@
         <v>USER_APPLICATION_POLICY</v>
       </c>
       <c r="F5" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="6">
@@ -1090,7 +1090,7 @@
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F6" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="7">
@@ -1110,7 +1110,7 @@
         <v>OFFICIAL_SOURCE_REVIEW</v>
       </c>
       <c r="F7" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="8">
@@ -1128,7 +1128,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F8" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="9">
@@ -1148,7 +1148,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F9" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="10">
@@ -1168,7 +1168,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F10" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="11">
@@ -1188,7 +1188,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F11" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="12">
@@ -1208,7 +1208,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F12" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="13">
@@ -1228,7 +1228,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F13" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="14">
@@ -1248,7 +1248,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F14" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="15">
@@ -1266,7 +1266,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F15" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="16">
@@ -1284,7 +1284,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F16" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F17" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="18">
@@ -1324,7 +1324,7 @@
         <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F18" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="19">
@@ -1344,7 +1344,7 @@
         <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F19" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="20">
@@ -1364,7 +1364,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F20" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="21">
@@ -1384,7 +1384,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F21" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="22">
@@ -1398,13 +1398,13 @@
         <v>window_type,frame_type</v>
       </c>
       <c r="D22" t="str" s="36">
-        <v>{"label": "ガラス種類", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス種類", "group": "glazing", "internal": false, "rank": 1}</v>
       </c>
       <c r="E22" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F22" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="23">
@@ -1415,16 +1415,16 @@
         <v>glass</v>
       </c>
       <c r="C23" t="str" s="36">
-        <v>glass_category,window_type,frame_type</v>
+        <v>glass_category,glass_appearance,window_type,frame_type</v>
       </c>
       <c r="D23" t="str" s="36">
-        <v>{"label": "ガラス詳細・Low-E仕様", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス詳細・Low-E仕様", "group": "glazing", "internal": false, "rank": 3}</v>
       </c>
       <c r="E23" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F23" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="24">
@@ -1444,7 +1444,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F24" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="25">
@@ -1464,7 +1464,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F25" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="26">
@@ -1475,16 +1475,16 @@
         <v>glass_function</v>
       </c>
       <c r="C26" t="str" s="36">
-        <v>glass_category,glass,window_type</v>
+        <v>glass_category,glass_appearance,glass,window_type</v>
       </c>
       <c r="D26" t="str" s="36">
-        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス追加機能", "group": "glazing", "internal": false, "rank": 4}</v>
       </c>
       <c r="E26" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F26" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="27">
@@ -1495,16 +1495,16 @@
         <v>glass_appearance</v>
       </c>
       <c r="C27" t="str" s="36">
-        <v>glass,glass_function</v>
+        <v>glass_category</v>
       </c>
       <c r="D27" t="str" s="36">
-        <v>{"label": "ガラス仕上げ・目隠し", "group": "glazing", "internal": false}</v>
+        <v>{"label": "ガラス種", "group": "glazing", "internal": false, "rank": 2}</v>
       </c>
       <c r="E27" t="str" s="37">
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F27" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="28">
@@ -1522,7 +1522,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F28" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="29">
@@ -1540,7 +1540,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F29" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="30">
@@ -1560,7 +1560,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F30" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="31">
@@ -1580,7 +1580,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F31" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="32">
@@ -1600,7 +1600,7 @@
         <v>USER_PRESENTATION_POLICY</v>
       </c>
       <c r="F32" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="33">
@@ -1618,7 +1618,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F33" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="34">
@@ -1638,7 +1638,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F34" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="35">
@@ -1658,7 +1658,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F35" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="36">
@@ -1678,7 +1678,7 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F36" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
     <row r="37">
@@ -1698,7 +1698,67 @@
         <v>UI_PRESENTATION</v>
       </c>
       <c r="F37" t="str">
-        <v>REPLUS_HIDE_DERIVED_CONFIRMATIONS_V12_20261014</v>
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>FIELD_PATCH</v>
+      </c>
+      <c r="B38" t="str">
+        <v>glass_appearance</v>
+      </c>
+      <c r="C38" t="str">
+        <v>glass_category</v>
+      </c>
+      <c r="D38" t="str">
+        <v>{"key": "glass_appearance", "displayLabel": "ガラス種", "dataType": "ENUM", "displayOrder": 710, "required": false, "autoSelectSingle": false, "parentFields": ["glass_category"], "selector": {"glass_category": {"$exists": true}}, "choices": [{"value": "MILKY", "displayLabel": "乳白", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 4}, {"value": "CLEAR", "displayLabel": "透明", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 1}, {"value": "OBSCURE", "displayLabel": "型板", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 2}, {"value": "FROST", "displayLabel": "フロスト", "selector": {"glass_category": {"$exists": true}}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 3}]}</v>
+      </c>
+      <c r="E38" t="str">
+        <v>USER_FLOW_POLICY_WITH_EXISTING_EVIDENCE</v>
+      </c>
+      <c r="F38" t="str">
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>FIELD_PATCH</v>
+      </c>
+      <c r="B39" t="str">
+        <v>glass</v>
+      </c>
+      <c r="C39" t="str">
+        <v>glass_category,glass_appearance,window_type,frame_type</v>
+      </c>
+      <c r="D39" t="str">
+        <v>{"key": "glass", "displayLabel": "ガラス詳細・Low-E仕様", "dataType": "ENUM", "displayOrder": 720, "choices": [{"value": "GL-PG", "displayLabel": "一般複層ガラス", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_SLD", "glass_category": "複層ガラス", "not": {"frame_type": "RPL_BRIDGE"}}, "metadata": {"manualCheck": true}}, {"value": "GL-PG", "displayLabel": "一般複層ガラス", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_VS_OP", "glass_category": "複層ガラス", "not": {"frame_type": "RPL_BRIDGE"}}, "metadata": {"manualCheck": true}}, {"value": "GL-PG", "displayLabel": "一般複層ガラス", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_VS_CAM", "glass_category": "複層ガラス", "not": {"frame_type": "RPL_BRIDGE"}}, "metadata": {"manualCheck": true}}, {"value": "GL-PG", "displayLabel": "一般複層ガラス", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_HS_OP", "glass_category": "複層ガラス", "not": {"frame_type": "RPL_BRIDGE"}}, "metadata": {"manualCheck": true}}, {"value": "GL-PG", "displayLabel": "一般複層ガラス", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_HS_CAM", "glass_category": "複層ガラス", "not": {"frame_type": "RPL_BRIDGE"}}, "metadata": {"manualCheck": true}}, {"value": "GL-PG", "displayLabel": "一般複層ガラス", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_FIX_OUT", "glass_category": "複層ガラス", "not": {"frame_type": "RPL_BRIDGE"}}, "metadata": {"manualCheck": true}}, {"value": "GL-PG", "displayLabel": "一般複層ガラス", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_FIX_IN", "glass_category": "複層ガラス", "not": {"frame_type": "RPL_BRIDGE"}}, "metadata": {"manualCheck": true}}, {"value": "GL-PG", "displayLabel": "一般複層ガラス", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_DHFS", "glass_category": "複層ガラス", "not": {"frame_type": "RPL_BRIDGE"}}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-CLEAR", "displayLabel": "Low-E複層ガラス クリア", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_SLD", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-CLEAR", "displayLabel": "Low-E複層ガラス クリア", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_VS_OP", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-CLEAR", "displayLabel": "Low-E複層ガラス クリア", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_VS_CAM", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-CLEAR", "displayLabel": "Low-E複層ガラス クリア", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_HS_OP", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-CLEAR", "displayLabel": "Low-E複層ガラス クリア", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_HS_CAM", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-CLEAR", "displayLabel": "Low-E複層ガラス クリア", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_FIX_OUT", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-CLEAR", "displayLabel": "Low-E複層ガラス クリア", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_FIX_IN", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-CLEAR", "displayLabel": "Low-E複層ガラス クリア", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_DHFS", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN", "displayLabel": "Low-E複層ガラス グリーン", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_SLD", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN", "displayLabel": "Low-E複層ガラス グリーン", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_VS_OP", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN", "displayLabel": "Low-E複層ガラス グリーン", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_VS_CAM", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN", "displayLabel": "Low-E複層ガラス グリーン", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_HS_OP", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN", "displayLabel": "Low-E複層ガラス グリーン", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_HS_CAM", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN", "displayLabel": "Low-E複層ガラス グリーン", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_FIX_OUT", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN", "displayLabel": "Low-E複層ガラス グリーン", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_FIX_IN", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN", "displayLabel": "Low-E複層ガラス グリーン", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_DHFS", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN-HS", "displayLabel": "Low-E複層ガラス グリーン（高遮熱仕様）", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_SLD", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN-HS", "displayLabel": "Low-E複層ガラス グリーン（高遮熱仕様）", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_VS_OP", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN-HS", "displayLabel": "Low-E複層ガラス グリーン（高遮熱仕様）", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_VS_CAM", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN-HS", "displayLabel": "Low-E複層ガラス グリーン（高遮熱仕様）", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_HS_OP", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN-HS", "displayLabel": "Low-E複層ガラス グリーン（高遮熱仕様）", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_HS_CAM", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN-HS", "displayLabel": "Low-E複層ガラス グリーン（高遮熱仕様）", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_FIX_OUT", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN-HS", "displayLabel": "Low-E複層ガラス グリーン（高遮熱仕様）", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_FIX_IN", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-LOWE-GREEN-HS", "displayLabel": "Low-E複層ガラス グリーン（高遮熱仕様）", "evidenceIds": ["EV-020"], "selector": {"window_type": "RPL_ROOM_DHFS", "glass_category": "Low-E複層ガラス"}, "metadata": {"manualCheck": true}}, {"value": "GL-TRIPLE-DHFS", "displayLabel": "トリプルガラス", "evidenceIds": ["EV-014,020"], "selector": {"window_type": "RPL_ROOM_DHFS", "glass_category": "トリプル"}, "metadata": {"manualCheck": true}}], "required": false, "autoSelectSingle": false, "parentFields": ["glass_category", "glass_appearance", "window_type", "frame_type"], "selector": {"glass_category": {"$exists": true}}}</v>
+      </c>
+      <c r="E39" t="str">
+        <v>USER_FLOW_POLICY_WITH_EXISTING_EVIDENCE</v>
+      </c>
+      <c r="F39" t="str">
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>FIELD_PATCH</v>
+      </c>
+      <c r="B40" t="str">
+        <v>glass_function</v>
+      </c>
+      <c r="C40" t="str">
+        <v>glass_category,glass_appearance,glass,window_type</v>
+      </c>
+      <c r="D40" t="str">
+        <v>{"key": "glass_function", "displayLabel": "ガラス追加機能", "dataType": "ENUM", "displayOrder": 730, "required": false, "autoSelectSingle": false, "parentFields": ["glass_category", "glass_appearance", "glass", "window_type"], "selector": {"glass": {"$exists": true}}, "choices": [{"value": "NONE", "displayLabel": "なし（標準）", "selector": {"all": [{"glass_category": "複層ガラス", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": false, "estimateConfirmationRequired": false}, "displayOrder": 1}, {"value": "GL-SAFETY", "displayLabel": "安全合わせ", "selector": {"all": [{"glass_category": "複層ガラス", "glass": {"$exists": true}, "window_type": {"$in": ["RPL_ROOM_SLD", "RPL_ROOM_VS_OP", "RPL_ROOM_VS_CAM", "RPL_ROOM_HS_OP", "RPL_ROOM_HS_CAM", "RPL_ROOM_DHFS"]}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 2}, {"value": "DISASTER", "displayLabel": "防災安全合わせ", "selector": {"all": [{"glass_category": "複層ガラス", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 3}, {"value": "MILKY", "displayLabel": "安全合わせ乳白タイプ", "selector": {"all": [{"glass_category": "複層ガラス", "glass": {"$exists": true}}, {"glass_appearance": "MILKY"}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 4}, {"value": "GRID", "displayLabel": "格子入り", "selector": {"all": [{"glass_category": "複層ガラス", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 5}, {"value": "BLIND", "displayLabel": "ブラインドインPG", "selector": {"all": [{"glass_category": "複層ガラス", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 6}, {"value": "NONE", "displayLabel": "なし（標準）", "selector": {"all": [{"glass_category": "Low-E複層ガラス", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": false, "estimateConfirmationRequired": false}, "displayOrder": 1}, {"value": "GL-SAFETY", "displayLabel": "安全合わせ", "selector": {"all": [{"glass_category": "Low-E複層ガラス", "glass": {"$exists": true}, "window_type": {"$in": ["RPL_ROOM_SLD", "RPL_ROOM_VS_OP", "RPL_ROOM_VS_CAM", "RPL_ROOM_HS_OP", "RPL_ROOM_HS_CAM", "RPL_ROOM_DHFS"]}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 2}, {"value": "DISASTER", "displayLabel": "防災安全合わせ", "selector": {"all": [{"glass_category": "Low-E複層ガラス", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 3}, {"value": "MILKY", "displayLabel": "安全合わせ乳白タイプ", "selector": {"all": [{"glass_category": "Low-E複層ガラス", "glass": {"$exists": true}}, {"glass_appearance": "MILKY"}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 4}, {"value": "GRID", "displayLabel": "格子入り", "selector": {"all": [{"glass_category": "Low-E複層ガラス", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 5}, {"value": "BLIND", "displayLabel": "ブラインドインPG", "selector": {"all": [{"glass_category": "Low-E複層ガラス", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 6}, {"value": "NONE", "displayLabel": "なし（標準）", "selector": {"all": [{"glass_category": "トリプル", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": false, "estimateConfirmationRequired": false}, "displayOrder": 1}, {"value": "GL-SAFETY", "displayLabel": "安全合わせ", "selector": {"all": [{"glass_category": "トリプル", "glass": {"$exists": true}, "window_type": {"$in": ["RPL_ROOM_SLD", "RPL_ROOM_VS_OP", "RPL_ROOM_VS_CAM", "RPL_ROOM_HS_OP", "RPL_ROOM_HS_CAM", "RPL_ROOM_DHFS"]}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 2}, {"value": "DISASTER", "displayLabel": "防災安全合わせ", "selector": {"all": [{"glass_category": "トリプル", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 3}, {"value": "MILKY", "displayLabel": "安全合わせ乳白タイプ", "selector": {"all": [{"glass_category": "トリプル", "glass": {"$exists": true}}, {"glass_appearance": "MILKY"}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 4}, {"value": "THIN", "displayLabel": "特殊薄板合わせ", "selector": {"all": [{"glass_category": "トリプル", "glass": {"$exists": true}}, {"not": {"glass_appearance": "MILKY"}}]}, "evidenceIds": ["EV-V8-GLASS-DIAGRAM"], "metadata": {"manualCheck": true, "estimateConfirmationRequired": true}, "displayOrder": 7}]}</v>
+      </c>
+      <c r="E40" t="str">
+        <v>USER_FLOW_POLICY_WITH_EXISTING_EVIDENCE</v>
+      </c>
+      <c r="F40" t="str">
+        <v>REPLUS_GLASS_APPEARANCE_FIRST_V13_20261014</v>
       </c>
     </row>
   </sheetData>
